--- a/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
+++ b/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Трубопроводы (модель)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Трубопроводы" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Кабели" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -570,7 +570,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>аналог — CDLF 1-...(CNP)</t>
+          <t>по опросному листу; аналог — серия CDLF (CNP)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Ороситель спринклерный водяной розеткой вниз, K=0,42 л/(с·МПа^0,5), tраб=68 °C, присоединение R1/2</t>
+          <t>Ороситель спринклерный водяной розеткой вниз, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Ороситель спринклерный водяной розеткой вверх, K=0,42 л/(с·МПа^0,5), tраб=68 °C, присоединение R1/2</t>
+          <t>Ороситель спринклерный водяной розеткой вверх, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4380,7 +4380,7 @@
       <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>S≈702 м²</t>
+          <t>S=702 м²</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Длина по модели, м</t>
+          <t>Длина, м</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>МПП-1…МПП-4 (цепь пуска)</t>
+          <t>МПП-1...МПП-4 (цепь пуска)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">

--- a/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
+++ b/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I173"/>
+  <dimension ref="A1:I212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1. Насосная станция пожаротушения (пом. 05)</t>
+          <t>1. Насосная станция пожаротушения (технический подвал, оси 1–2/Д–Е)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Насос центробежный вертикальный (in-line) для систем пожаротушения, Q=145 м³/ч, H=32 м, N=22 кВт, 380 В, 2900 об/мин, фланцы Ду100 PN16 (Н1 — рабочий, Н2 — резервный)</t>
+          <t>Насос центробежный вертикальный (in-line) для систем пожаротушения, Q=145 м³/ч, H=21 м, N=15 кВт, 380 В, 2900 об/мин, фланцы Ду125 PN16 (Н1 — рабочий, Н2 — резервный)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -551,7 +551,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Насос вертикальный многоступенчатый (жокей-насос) Н3, Q=1,5 м³/ч, H=45 м, N=0,75 кВт, 380 В</t>
+          <t>Насос вертикальный многоступенчатый (жокей-насос) Н3, Q=1,5 м³/ч, H=30 м, N=0,55 кВт, 380 В</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -584,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
@@ -676,14 +676,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>вводы, обвод, после УУ</t>
+          <t>вводы, обвод, Н1, Н2, после УУ</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,16 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>опробование, отвод ВПВ, ГМ-80</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -738,14 +742,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>9</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>вводы, обвод</t>
+          <t>вводы, обвод, Н1, Н2</t>
         </is>
       </c>
     </row>
@@ -771,14 +775,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>4.5</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>насосы, патрубки ГМ-80</t>
+          <t>патрубки ГМ-80</t>
         </is>
       </c>
     </row>
@@ -788,12 +792,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Компенсатор резиновый фланцевый (виброкомпенсатор) Ду100 PN16</t>
+          <t>Компенсатор резиновый фланцевый (виброкомпенсатор) Ду125 PN16</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -807,9 +811,13 @@
         <v>4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Н1, Н2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -817,12 +825,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной эксцентрический приварной 159×4,5–108×4</t>
+          <t>Переход стальной эксцентрический приварной 159×4,5–133×4</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ПЭ 159×4,5-108×4, ГОСТ 17378-2001</t>
+          <t>ПЭ 159×4,5-133×4, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -836,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
@@ -850,12 +858,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический приварной 159×4,5–108×4</t>
+          <t>Переход стальной концентрический приварной 159×4,5–133×4</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ПК 159×4,5-108×4, ГОСТ 17378-2001</t>
+          <t>ПК 159×4,5-133×4, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -869,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -961,12 +969,16 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>вводы, Н1–Н3, коллекторы</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1153,106 +1165,112 @@
       <c r="I24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>2. Автоматическая установка водяного пожаротушения. Секция 1 — В21 (1 этаж), секция 2 — В22 (2 этаж)</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Насос дренажный погружной для чистой и слабозагрязнённой воды, Q=10 м³/ч, H=10 м, N=0,75 кВт, 380 В, с поплавковым выключателем (ДН1 — рабочий, ДН2 — резервный)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>по опросному листу; аналог — «Гном 10-10»</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>приямок насосной</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Ороситель спринклерный водяной розеткой вниз, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
+          <t>Шкаф управления дренажными насосами: поочерёдная работа, включение резервного, сигнал «Аварийный уровень» (сухой контакт)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>СВО0-РНо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
+          <t>по опросному листу</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>ПО «Спецавтоматика» или аналог</t>
-        </is>
-      </c>
+      <c r="E26" s="3" t="inlineStr"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>секция 1</t>
+          <t>насосная</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Ороситель спринклерный водяной розеткой вверх, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>СВО0-РВо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
-        </is>
-      </c>
+          <t>Выключатель поплавковый (уровни «пуск», «стоп», «аварийный»)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>ПО «Спецавтоматика» или аналог</t>
-        </is>
-      </c>
+      <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>462</v>
+        <v>3</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>секция 2</t>
+          <t>приямок</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Оросители запасные (10 % от смонтированных) в шкафу для хранения с ключом монтажным</t>
+          <t>Клапан обратный пружинный муфтовый Ду40 PN16</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>то же</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -1263,27 +1281,31 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>50 РНо + 47 РВо</t>
+          <t>ДН1, ДН2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Шкаф для хранения запасных оросителей</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr"/>
+          <t>Кран шаровой стальной муфтовый Ду40 PN16</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Ду40</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
@@ -1292,107 +1314,89 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>пом. 05</t>
+          <t>ДН1, ДН2, выпуск</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Узел промывки и опорожнения в конце питающего трубопровода: кран шаровой Ду50, заглушка G2" с цепочкой</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>см. узел 8</t>
-        </is>
-      </c>
+          <t>Решётка стальная оцинкованная съёмная для приямка 1000×1000, ячейка 30×30, нагрузка 3 кН/м²</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="inlineStr"/>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Узел опробования в диктующей точке секции: кран шаровой Ду25, манометр МП-100 0–1,0 МПа, насадок K=0,42</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>см. узел 9</t>
-        </is>
-      </c>
+          <t>Виброизолятор резинометаллический под раму насоса</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>4 на насос</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Воздухоотводчик автоматический Ду15 PN16 с запорным краном</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Ду15</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>в верхних точках питающих</t>
-        </is>
-      </c>
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>1а. Трубопроводы и фасонные части обвязки насосной</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -1400,56 +1404,78 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Бобышка (муфта) стальная приварная G1/2 для присоединения оросителя</t>
+          <t>Труба стальная электросварная прямошовная 219×6,0</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>G1/2</t>
+          <t>219×6,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>958</v>
+        <v>8</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
+        <v>31.52</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>всасывающий и напорный коллекторы</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>3. Трубопроводы и фасонные части системы В21 (секция 1)</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
+      <c r="A34" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная прямошовная 159×4,5</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>вводы, линии Н1, Н2, обвод, УУ</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду25×3,2</t>
+          <t>Труба стальная электросварная прямошовная 133×4,0</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>33,5×3,2, ГОСТ 3262-75</t>
+          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1460,29 +1486,29 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>463</v>
+        <v>3</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.39</v>
+        <v>12.73</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>с запасом 5 %</t>
+          <t>у насосов</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
+          <t>Труба стальная электросварная прямошовная 108×4,0</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>42,3×3,2, ГОСТ 3262-75</t>
+          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1493,29 +1519,29 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3.09</v>
+        <v>10.26</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>с запасом 5 %</t>
+          <t>опробование, линия к ГМ-80</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>48×3,5, ГОСТ 3262-75</t>
+          <t>60×3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1526,29 +1552,29 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>286</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>3.84</v>
+        <v>4.88</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>с запасом 5 %</t>
+          <t>дренаж УУ, выпуск дренажных насосов</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>60×3,5, ГОСТ 3262-75</t>
+          <t>48×3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1559,29 +1585,29 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>400</v>
+        <v>4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4.88</v>
+        <v>3.84</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>с запасом 5 %</t>
+          <t>напорные ДН1, ДН2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>42,3×3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1592,161 +1618,141 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>6.26</v>
+        <v>3.09</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>с запасом 5 %</t>
+          <t>обвязка Н3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 219×6,0</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108×4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133×4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 108×4,0</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 159×4,5</t>
+          <t>Тройник стальной приварной 219×6,0 с ответвлением 159×4,5</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>17.15</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>с запасом 5 %</t>
+          <t>врезки в коллекторы</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной Ду50×Ду32 (сварной/резьбовой)</t>
+          <t>Тройник стальной приварной 219×6,0 с ответвлением 108×4,0</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 8948-75 / сварка</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1757,23 +1763,23 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76×3,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Заглушка стальная эллиптическая 219×6,0</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17379-2001</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1784,118 +1790,118 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>торцы коллекторов</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 89×3,5 с ответвлением 33,5×3,2 (врезка)</t>
+          <t>Фланец стальной плоский приварной Ду150 PN16 (комплект с крепежом и прокладками)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>под арматуру</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 89×3,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Фланец стальной плоский приварной Ду100 PN16 (комплект с крепежом и прокладками)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108×4,0 с ответвлением 60×3,5 (врезка)</t>
+          <t>Фланец стальной плоский приварной Ду125 PN16 (комплект с крепежом и прокладками)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>насосы, компенсаторы</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Тройник стальной приварной 133×4,0 с ответвлением 60×3,5 (врезка)</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>, ГОСТ 17376-2001</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2. Автоматическая установка водяного пожаротушения. Секция 1 — В21 (1 этаж), секция 2 — В22 (2 этаж)</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
       <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -1903,26 +1909,36 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133×4,0 с ответвлением 76×3,5 (врезка)</t>
+          <t>Ороситель спринклерный водяной розеткой вниз, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>СВО0-РНо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ПО «Спецавтоматика» или аналог</t>
+        </is>
+      </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>секция 1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -1930,26 +1946,36 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 42,3×3,2 (врезка)</t>
+          <t>Ороситель спринклерный водяной розеткой вверх, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>СВО0-РВо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ПО «Спецавтоматика» или аналог</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="inlineStr"/>
+        <v>462</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>секция 2</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -1957,12 +1983,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Оросители запасные (10 % от смонтированных) в шкафу для хранения с ключом монтажным</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>то же</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1973,10 +1999,16 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>50 РНо + 47 РВо</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -1984,14 +2016,10 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 76×3,5 (врезка)</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>, ГОСТ 17376-2001</t>
-        </is>
-      </c>
+          <t>Шкаф для хранения запасных оросителей</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr"/>
       <c r="D53" s="3" t="inlineStr"/>
       <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr">
@@ -2000,10 +2028,16 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>насосная</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -2011,25 +2045,27 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 133×4,0 (врезка)</t>
+          <t>Узел промывки и опорожнения в конце питающего трубопровода: кран шаровой Ду50, заглушка G2" с цепочкой</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>см. узел 8</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="I54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2038,25 +2074,27 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5</t>
+          <t>Узел опробования в диктующей точке секции: кран шаровой Ду25, манометр МП-100 0–1,0 МПа, насадок K=0,42</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>см. узел 9</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2065,12 +2103,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 33,5×3,2</t>
+          <t>Воздухоотводчик автоматический Ду15 PN16 с запорным краном</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>Ду15</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -2081,10 +2119,16 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>в верхних точках питающих</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -2092,12 +2136,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 42,3×3,2</t>
+          <t>Бобышка (муфта) стальная приварная G1/2 для присоединения оросителя</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>G1/2</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -2108,293 +2152,337 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
+        <v>962</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0.08</v>
+      </c>
       <c r="I57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Отвод стальной крутоизогнутый 90° 60×3,5</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>, ГОСТ 17375-2001</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>3. Трубопроводы и фасонные части системы В21 (секция 1)</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
       <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 76×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду25×3,2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>33,5×3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="inlineStr"/>
+        <v>474</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 133×4,0</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>42,3×3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr"/>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="inlineStr"/>
+        <v>318</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>48×3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="inlineStr"/>
+        <v>286</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 42,3×3,2–33,5×3,2</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>60×3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="inlineStr"/>
+        <v>404</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 48×3,5–42,3×3,2</t>
+          <t>Труба стальная электросварная прямошовная 76×3,5</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60×3,5–42,3×3,2</t>
+          <t>Труба стальная электросварная прямошовная 89×3,5</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
       <c r="E64" s="3" t="inlineStr"/>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60×3,5–48×3,5</t>
+          <t>Труба стальная электросварная прямошовная 108×4,0</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
       <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 76×3,5–60×3,5</t>
+          <t>Труба стальная электросварная прямошовная 133×4,0</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="3" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
+          <t>Труба стальная электросварная прямошовная 159×4,5</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
       <c r="E67" s="3" t="inlineStr"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 108×4,0–76×3,5</t>
+          <t>Тройник стальной Ду50×Ду32 (сварной/резьбовой)</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 8948-75 / сварка</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
@@ -2405,23 +2493,23 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133×4,0–89×3,5</t>
+          <t>Тройник стальной приварной 76×3,5 с ответвлением 60×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
@@ -2432,23 +2520,23 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133×4,0–108×4,0</t>
+          <t>Тройник стальной приварной 89×3,5 с ответвлением 33,5×3,2 (врезка)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -2466,16 +2554,16 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 159×4,5–133×4,0</t>
+          <t>Тройник стальной приварной 89×3,5 с ответвлением 60×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr"/>
@@ -2486,25 +2574,37 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>4. Трубопроводы и фасонные части системы В22 (секция 2)</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
+      <c r="A72" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Тройник стальной приварной 108×4,0 с ответвлением 60×3,5 (врезка)</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17376-2001</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
+      <c r="I72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -2512,32 +2612,26 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду25×3,2</t>
+          <t>Тройник стальной приварной 133×4,0 с ответвлением 60×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>33,5×3,2, ГОСТ 3262-75</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr"/>
       <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>505</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -2545,32 +2639,26 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
+          <t>Тройник стальной приварной 133×4,0 с ответвлением 76×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>42,3×3,2, ГОСТ 3262-75</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
       <c r="E74" s="3" t="inlineStr"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>378</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -2578,32 +2666,26 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
+          <t>Тройник стальной приварной 159×4,5 с ответвлением 42,3×3,2 (врезка)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>48×3,5, ГОСТ 3262-75</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
       <c r="E75" s="3" t="inlineStr"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -2611,32 +2693,26 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
+          <t>Тройник стальной приварной 159×4,5 с ответвлением 60×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>60×3,5, ГОСТ 3262-75</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
       <c r="E76" s="3" t="inlineStr"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -2644,32 +2720,26 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76×3,5</t>
+          <t>Тройник стальной приварной 159×4,5 с ответвлением 76×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
       <c r="E77" s="3" t="inlineStr"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -2677,32 +2747,26 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89×3,5</t>
+          <t>Тройник стальной приварной 159×4,5 с ответвлением 133×4,0 (врезка)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -2710,32 +2774,26 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133×4,0</t>
+          <t>Тройник стальной приварной 159×4,5</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr"/>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H79" s="3" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -2743,32 +2801,26 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 159×4,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 33,5×3,2</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
       <c r="E80" s="3" t="inlineStr"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>214</v>
-      </c>
-      <c r="H80" s="3" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -2776,12 +2828,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76×3,5 с ответвлением 42,3×3,2 (врезка)</t>
+          <t>Отвод стальной крутоизогнутый 90° 42,3×3,2</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -2792,7 +2844,7 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="inlineStr"/>
@@ -2803,12 +2855,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76×3,5 с ответвлением 48×3,5 (врезка)</t>
+          <t>Отвод стальной крутоизогнутый 90° 60×3,5</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr"/>
@@ -2819,7 +2871,7 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="inlineStr"/>
@@ -2830,12 +2882,12 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133×4,0 с ответвлением 76×3,5 (врезка)</t>
+          <t>Отвод стальной крутоизогнутый 90° 76×3,5</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr"/>
@@ -2846,7 +2898,7 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="inlineStr"/>
@@ -2857,12 +2909,12 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Отвод стальной крутоизогнутый 90° 133×4,0</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr"/>
@@ -2873,7 +2925,7 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="inlineStr"/>
@@ -2884,12 +2936,12 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 76×3,5 (врезка)</t>
+          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr"/>
@@ -2900,7 +2952,7 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="inlineStr"/>
@@ -2911,12 +2963,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 89×3,5 (врезка)</t>
+          <t>Переход стальной концентрический 42,3×3,2–33,5×3,2</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2927,7 +2979,7 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="inlineStr"/>
@@ -2938,12 +2990,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5</t>
+          <t>Переход стальной концентрический 48×3,5–42,3×3,2</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
@@ -2954,7 +3006,7 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="inlineStr"/>
@@ -2965,12 +3017,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 33,5×3,2</t>
+          <t>Переход стальной концентрический 60×3,5–42,3×3,2</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
@@ -2981,7 +3033,7 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="inlineStr"/>
@@ -2992,12 +3044,12 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 60×3,5</t>
+          <t>Переход стальной концентрический 60×3,5–48×3,5</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
@@ -3008,7 +3060,7 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="inlineStr"/>
@@ -3019,12 +3071,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 89×3,5</t>
+          <t>Переход стальной концентрический 76×3,5–60×3,5</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
@@ -3035,7 +3087,7 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="inlineStr"/>
@@ -3046,12 +3098,12 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
+          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
@@ -3073,7 +3125,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 42,3×3,2–33,5×3,2</t>
+          <t>Переход стальной концентрический 108×4,0–76×3,5</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3089,7 +3141,7 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="inlineStr"/>
@@ -3100,7 +3152,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 48×3,5–42,3×3,2</t>
+          <t>Переход стальной концентрический 133×4,0–89×3,5</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3116,7 +3168,7 @@
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="inlineStr"/>
@@ -3127,7 +3179,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60×3,5–48×3,5</t>
+          <t>Переход стальной концентрический 133×4,0–108×4,0</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3143,7 +3195,7 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="H94" s="3" t="n"/>
       <c r="I94" s="3" t="inlineStr"/>
@@ -3154,7 +3206,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 76×3,5–60×3,5</t>
+          <t>Переход стальной концентрический 159×4,5–133×4,0</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3170,106 +3222,124 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>, ГОСТ 17378-2001</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" s="3" t="inlineStr"/>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>4</v>
-      </c>
+      <c r="A96" s="3" t="inlineStr"/>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>4. Трубопроводы и фасонные части системы В22 (секция 2)</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n"/>
+      <c r="D96" s="3" t="n"/>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
       <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133×4,0–89×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду25×3,2</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>33,5×3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
       <c r="E97" s="3" t="inlineStr"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="inlineStr"/>
+        <v>506</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 159×4,5–133×4,0</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>42,3×3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
       <c r="E98" s="3" t="inlineStr"/>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="inlineStr"/>
+        <v>378</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr"/>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>5. Внутренний противопожарный водопровод — В2</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="n"/>
-      <c r="D99" s="3" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n"/>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
+      <c r="A99" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>48×3,5, ГОСТ 3262-75</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -3277,30 +3347,30 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Шкаф пожарный навесной закрытый для двух пожарных кранов Ду65 и двух огнетушителей, с окном и местом для кнопки дистанционного пуска</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>ШПК-320-21НЗК</t>
+          <t>60×3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
       <c r="E100" s="3" t="inlineStr"/>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>38</v>
+        <v>4.88</v>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>огнетушители — по разделу ПБ</t>
+          <t>с запасом 5 %</t>
         </is>
       </c>
     </row>
@@ -3310,28 +3380,32 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Клапан пожарный запорный угловой 125° латунный Ду65 с головкой соединительной ГМ-65</t>
+          <t>Труба стальная электросварная прямошовная 76×3,5</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>КПЛМ 65-1, ГОСТ Р 53278-2009</t>
+          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I101" s="3" t="inlineStr"/>
+        <v>6.26</v>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -3339,28 +3413,32 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Рукав пожарный напорный Ду65, L=20 м, рабочее давление 1,6 МПа, с головками ГР-65</t>
+          <t>Труба стальная электросварная прямошовная 89×3,5</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Ду65 L=20 м, ГОСТ Р 51049-2019</t>
+          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
       <c r="E102" s="3" t="inlineStr"/>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I102" s="3" t="inlineStr"/>
+        <v>7.38</v>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -3368,28 +3446,32 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Ствол пожарный ручной с насадком Ø19 мм, головка ГР-70/65</t>
+          <t>Труба стальная электросварная прямошовная 133×4,0</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>РС-70 (насадок 19 мм), ГОСТ Р 53331-2009</t>
+          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I103" s="3" t="inlineStr"/>
+        <v>12.73</v>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -3397,30 +3479,30 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный межфланцевый Ду100 PN16 с рукояткой (секционирование кольца ВПВ)</t>
+          <t>Труба стальная электросварная прямошовная 159×4,5</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
       <c r="E104" s="3" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>10</v>
+        <v>217</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>6.5</v>
+        <v>17.15</v>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>опломбировать в открытом положении</t>
+          <t>с запасом 5 %</t>
         </is>
       </c>
     </row>
@@ -3430,20 +3512,16 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Устройство дистанционного пуска «Пуск насосов» (в шкафу ПК)</t>
+          <t>Тройник стальной приварной 76×3,5 с ответвлением 42,3×3,2 (врезка)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>ЭДУ 513-3АМ исп. 02 (зелёный)</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид» или аналог</t>
-        </is>
-      </c>
+      <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3452,9 +3530,7 @@
       <c r="G105" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="H105" s="3" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="H105" s="3" t="n"/>
       <c r="I105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3463,12 +3539,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Извещатель охранный магнитоконтактный (положение дверцы шкафа ПК)</t>
+          <t>Тройник стальной приварной 76×3,5 с ответвлением 48×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>ИО 102-20 Б2П</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr"/>
@@ -3479,134 +3555,126 @@
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>0.05</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H106" s="3" t="n"/>
       <c r="I106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr"/>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>6. Трубопроводы и фасонные части системы В2</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="n"/>
-      <c r="D107" s="3" t="n"/>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="3" t="n"/>
+      <c r="A107" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Тройник стальной приварной 133×4,0 с ответвлением 76×3,5 (врезка)</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17376-2001</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H107" s="3" t="n"/>
-      <c r="I107" s="3" t="n"/>
+      <c r="I107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76×3,5</t>
+          <t>Тройник стальной приварной 159×4,5 с ответвлением 60×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr"/>
       <c r="E108" s="3" t="inlineStr"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H108" s="3" t="n"/>
+      <c r="I108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89×3,5</t>
+          <t>Тройник стальной приварной 159×4,5 с ответвлением 76×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr"/>
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="H109" s="3" t="n"/>
+      <c r="I109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108×4,0</t>
+          <t>Тройник стальной приварной 159×4,5 с ответвлением 89×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr"/>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H110" s="3" t="n"/>
+      <c r="I110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108×4,0 с ответвлением 89×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159×4,5</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -3622,23 +3690,23 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H111" s="3" t="n"/>
       <c r="I111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108×4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 33,5×3,2</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr"/>
@@ -3649,18 +3717,18 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="H112" s="3" t="n"/>
       <c r="I112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 89×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 60×3,5</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -3676,18 +3744,18 @@
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="H113" s="3" t="n"/>
       <c r="I113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 108×4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 89×3,5</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -3703,23 +3771,23 @@
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr"/>
@@ -3730,317 +3798,289 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr"/>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>7. Изделия и материалы (системы В2, В21, В22)</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n"/>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n"/>
-      <c r="G116" s="3" t="n"/>
+      <c r="A116" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Переход стальной концентрический 42,3×3,2–33,5×3,2</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17378-2001</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr"/>
+      <c r="E116" s="3" t="inlineStr"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>140</v>
+      </c>
       <c r="H116" s="3" t="n"/>
-      <c r="I116" s="3" t="n"/>
+      <c r="I116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду25, шпилька М10, гайка соединительная, анкер клиновой</t>
+          <t>Переход стальной концентрический 48×3,5–42,3×3,2</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr"/>
       <c r="E117" s="3" t="inlineStr"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>276</v>
+        <v>110</v>
       </c>
       <c r="H117" s="3" t="n"/>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+      <c r="I117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду32, шпилька М10, гайка соединительная, анкер клиновой</t>
+          <t>Переход стальной концентрический 60×3,5–48×3,5</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr"/>
       <c r="E118" s="3" t="inlineStr"/>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>220</v>
+        <v>72</v>
       </c>
       <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+      <c r="I118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду40, шпилька М10, гайка соединительная, анкер клиновой</t>
+          <t>Переход стальной концентрический 76×3,5–60×3,5</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr"/>
       <c r="E119" s="3" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="H119" s="3" t="n"/>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+      <c r="I119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду50, шпилька М10, гайка соединительная, анкер клиновой</t>
+          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr"/>
       <c r="E120" s="3" t="inlineStr"/>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>174</v>
+        <v>4</v>
       </c>
       <c r="H120" s="3" t="n"/>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+      <c r="I120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду65, шпилька М12, гайка соединительная, анкер клиновой</t>
+          <t>Переход стальной концентрический 133×4,0–89×3,5</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Ду65</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H121" s="3" t="n"/>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+      <c r="I121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду80, шпилька М12, гайка соединительная, анкер клиновой</t>
+          <t>Переход стальной концентрический 159×4,5–133×4,0</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr"/>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G122" s="3" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="H122" s="3" t="n"/>
-      <c r="I122" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+      <c r="I122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду100, шпилька М12, гайка соединительная, анкер клиновой</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>Ду100</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr"/>
-      <c r="E123" s="3" t="inlineStr"/>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>59</v>
-      </c>
+      <c r="A123" s="3" t="inlineStr"/>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>5. Внутренний противопожарный водопровод — В2</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n"/>
+      <c r="D123" s="3" t="n"/>
+      <c r="E123" s="3" t="n"/>
+      <c r="F123" s="3" t="n"/>
+      <c r="G123" s="3" t="n"/>
       <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+      <c r="I123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду125, шпилька М12, гайка соединительная, анкер клиновой</t>
+          <t>Шкаф пожарный навесной закрытый для двух пожарных кранов Ду65 и двух огнетушителей, с окном и местом для кнопки дистанционного пуска</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>ШПК-320-21НЗК</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr"/>
       <c r="E124" s="3" t="inlineStr"/>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H124" s="3" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>38</v>
+      </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>шаг — см. общие указания</t>
+          <t>огнетушители — по разделу ПБ</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Опора трубопровода: хомут с резиновым вкладышем Ду150, шпилька М12, гайка соединительная, анкер клиновой</t>
+          <t>Клапан пожарный запорный угловой 125° латунный Ду65 с головкой соединительной ГМ-65</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Ду150</t>
+          <t>КПЛМ 65-1, ГОСТ Р 53278-2009</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="H125" s="3" t="n"/>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>шаг — см. общие указания</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду25</t>
+          <t>Рукав пожарный напорный Ду65, L=20 м, рабочее давление 1,6 МПа, с головками ГР-65</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>Ду65 L=20 м, ГОСТ Р 51049-2019</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr"/>
@@ -4051,23 +4091,25 @@
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="H126" s="3" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="I126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду32</t>
+          <t>Ствол пожарный ручной с насадком Ø19 мм, головка ГР-70/65</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>РС-70 (насадок 19 мм), ГОСТ Р 53331-2009</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr"/>
@@ -4078,23 +4120,25 @@
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H127" s="3" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду40</t>
+          <t>Затвор дисковый поворотный межфланцевый Ду100 PN16 с рукояткой (секционирование кольца ВПВ)</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr"/>
@@ -4105,50 +4149,62 @@
         </is>
       </c>
       <c r="G128" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="H128" s="3" t="n"/>
-      <c r="I128" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>опломбировать в открытом положении</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду50</t>
+          <t>Устройство дистанционного пуска «Пуск насосов» (в шкафу ПК)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>ЭДУ 513-3АМ исп. 02 (зелёный)</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
-      <c r="E129" s="3" t="inlineStr"/>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид» или аналог</t>
+        </is>
+      </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="H129" s="3" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0.15</v>
+      </c>
       <c r="I129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду80</t>
+          <t>Извещатель охранный магнитоконтактный (положение дверцы шкафа ПК)</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>ИО 102-20 Б2П</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr"/>
@@ -4159,37 +4215,27 @@
         </is>
       </c>
       <c r="G130" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H130" s="3" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0.05</v>
+      </c>
       <c r="I130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду100</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>, см. узел 2</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr"/>
-      <c r="E131" s="3" t="inlineStr"/>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="A131" s="3" t="inlineStr"/>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>6. Трубопроводы и фасонные части системы В2</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n"/>
+      <c r="D131" s="3" t="n"/>
+      <c r="E131" s="3" t="n"/>
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="3" t="n"/>
       <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="inlineStr"/>
+      <c r="I131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
@@ -4197,26 +4243,32 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду125</t>
+          <t>Труба стальная электросварная прямошовная 76×3,5</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr"/>
       <c r="E132" s="3" t="inlineStr"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G132" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -4224,26 +4276,32 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду150</t>
+          <t>Труба стальная электросварная прямошовная 89×3,5</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
@@ -4251,26 +4309,32 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду80</t>
+          <t>Труба стальная электросварная прямошовная 108×4,0</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 3</t>
+          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
       <c r="E134" s="3" t="inlineStr"/>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G134" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
@@ -4278,12 +4342,12 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду100</t>
+          <t>Тройник стальной приварной 108×4,0 с ответвлением 76×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 3</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr"/>
@@ -4294,7 +4358,7 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H135" s="3" t="n"/>
       <c r="I135" s="3" t="inlineStr"/>
@@ -4305,12 +4369,12 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду150</t>
+          <t>Тройник стальной приварной 108×4,0 с ответвлением 89×3,5 (врезка)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 3</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr"/>
@@ -4321,7 +4385,7 @@
         </is>
       </c>
       <c r="G136" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H136" s="3" t="n"/>
       <c r="I136" s="3" t="inlineStr"/>
@@ -4332,26 +4396,26 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Состав огнезащитный терморасширяющийся (герметик) для заделки зазоров в гильзах, EI не ниже предела огнестойкости преграды</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr"/>
+          <t>Тройник стальной приварной 108×4,0</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17376-2001</t>
+        </is>
+      </c>
       <c r="D137" s="3" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="H137" s="3" t="n"/>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>0,25 кг на проход</t>
-        </is>
-      </c>
+      <c r="I137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -4359,30 +4423,26 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Грунтовка ГФ-021 (1 слой)</t>
+          <t>Отвод стальной крутоизогнутый 90° 89×3,5</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 25129-2020</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr"/>
       <c r="E138" s="3" t="inlineStr"/>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G138" s="3" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>S=702 м²</t>
-        </is>
-      </c>
+      <c r="I138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -4390,70 +4450,68 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 красная (2 слоя)</t>
+          <t>Отвод стальной крутоизогнутый 90° 108×4,0</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 6465-76</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr"/>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>8. Автоматическая установка порошкового пожаротушения помещения ВРУ (пом. 06)</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="n"/>
-      <c r="D140" s="3" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
+      <c r="A140" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17378-2001</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr"/>
+      <c r="E140" s="3" t="inlineStr"/>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>46</v>
+      </c>
       <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="n"/>
+      <c r="I140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>Модуль порошкового пожаротушения закачного типа, масса ОТВ 8 кг, защищаемый объём (класс В) не менее 32 м³, электропуск</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>МПП(Н)-8 (типа «Буран-8» или аналог), ГОСТ Р 53286-2009</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr"/>
-      <c r="E141" s="3" t="inlineStr"/>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I141" s="3" t="inlineStr"/>
+      <c r="A141" s="3" t="inlineStr"/>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>7. Узлы креплений трубопроводов (количество узлов в сборе)</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n"/>
+      <c r="D141" s="3" t="n"/>
+      <c r="E141" s="3" t="n"/>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
@@ -4461,30 +4519,28 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Запас модулей порошкового пожаротушения (100 %)</t>
+          <t>Узел крепления трубы Ду25 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>то же</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G142" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H142" s="3" t="n">
-        <v>13</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>хранение на объекте</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4494,34 +4550,28 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Блок управления пожаротушением на одно направление</t>
+          <t>Узел крепления трубы Ду32 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>С2000-АСПТ</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr"/>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>1.1</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>у входа в пом. 06</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4531,34 +4581,28 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Извещатель пожарный дымовой оптико-электронный адресно-аналоговый</t>
+          <t>Узел крепления трубы Ду40 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>ДИП-34А-04</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr"/>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E144" s="3" t="inlineStr"/>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G144" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H144" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>пуск по 2 из 3</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4568,34 +4612,28 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Устройство дистанционного пуска «Пуск порошка» (жёлтое, с защитной крышкой)</t>
+          <t>Узел крепления трубы Ду50 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>ЭДУ 513-3АМ исп. 01</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr"/>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H145" s="3" t="n">
-        <v>0.15</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H145" s="3" t="n"/>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>у входа</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4605,30 +4643,28 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «ПОРОШОК! УХОДИ!» 24 В</t>
+          <t>Узел крепления трубы Ду65 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Молния-24</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr"/>
       <c r="E146" s="3" t="inlineStr"/>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G146" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" s="3" t="n">
-        <v>0.25</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>внутри</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4638,30 +4674,28 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «ПОРОШОК! НЕ ВХОДИ!» 24 В</t>
+          <t>Узел крепления трубы Ду80 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Молния-24</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H147" s="3" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>над дверью снаружи</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4671,30 +4705,28 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «АВТОМАТИКА ОТКЛЮЧЕНА» 24 В</t>
+          <t>Узел крепления трубы Ду100 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Молния-24</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr"/>
       <c r="E148" s="3" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G148" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" s="3" t="n">
-        <v>0.25</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>снаружи</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4704,30 +4736,28 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Оповещатель звуковой 24 В, 105 дБ</t>
+          <t>Узел крепления трубы Ду125 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Маяк-24-3М</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H149" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>внутри</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
@@ -4737,28 +4767,30 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Извещатель магнитоконтактный (контроль закрытия двери)</t>
+          <t>Узел крепления трубы Ду150 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>ИО 102-26 «Аякс»</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr"/>
       <c r="E150" s="3" t="inlineStr"/>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G150" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I150" s="3" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -4766,32 +4798,30 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2×12 В 17 А·ч</t>
+          <t>Узел крепления трубы Ду65 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>РИП-24 исп. 01</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr"/>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
           <t>компл.</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I151" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -4799,245 +4829,233 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Коробка коммутационная огнестойкая (Е90)</t>
+          <t>Узел крепления трубы Ду80 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>КМ-О (4к)-IP41</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr"/>
       <c r="E152" s="3" t="inlineStr"/>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G152" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H152" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I152" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="H152" s="3" t="n"/>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr"/>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>9. Автоматизация систем водяного пожаротушения</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="n"/>
-      <c r="D153" s="3" t="n"/>
-      <c r="E153" s="3" t="n"/>
-      <c r="F153" s="3" t="n"/>
-      <c r="G153" s="3" t="n"/>
+      <c r="A153" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Узел крепления трубы Ду100 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>узел 4, тип 1</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr"/>
+      <c r="E153" s="3" t="inlineStr"/>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>48</v>
+      </c>
       <c r="H153" s="3" t="n"/>
-      <c r="I153" s="3" t="n"/>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Прибор управления насосной станцией пожаротушения (основной, резервный, жокей-насос)</t>
+          <t>Узел крепления трубы Ду25 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Поток-3Н</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr"/>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E154" s="3" t="inlineStr"/>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="H154" s="3" t="n"/>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>пом. 05</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Шкаф контрольно-пусковой для электродвигателя до 30 кВт, 380 В</t>
+          <t>Узел крепления трубы Ду32 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>ШКП-30</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr"/>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H155" s="3" t="n">
-        <v>25</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>Н1, Н2</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Шкаф контрольно-пусковой для электродвигателя до 4 кВт, 380 В</t>
+          <t>Узел крепления трубы Ду40 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>ШКП-4</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr"/>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E156" s="3" t="inlineStr"/>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G156" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" s="3" t="n">
-        <v>12</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>Н3</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Контроллер двухпроводной линии связи (адресные устройства ПТ)</t>
+          <t>Узел крепления трубы Ду50 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>С2000-КДЛ-2И</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr"/>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>RS-485 к ППКУП «Сириус»</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Адресный расширитель на 2 входа (контроль затворов, дверей шкафов ПК, кнопок «Пуск насосов»)</t>
+          <t>Узел крепления трубы Ду80 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>С2000-АР2 исп. 02</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr"/>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E158" s="3" t="inlineStr"/>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G158" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H158" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I158" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2×12 В 17 А·ч</t>
+          <t>Узел крепления трубы Ду125 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>РИП-24 исп. 01</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr"/>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
           <t>компл.</t>
@@ -5046,412 +5064,1575 @@
       <c r="G159" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H159" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I159" s="3" t="inlineStr"/>
+      <c r="H159" s="3" t="n"/>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Шкаф монтажный навесной 600×600×250 IP54 для приборов автоматики ПТ</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr"/>
+          <t>Узел крепления трубы Ду150 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>узел 4, тип 2</t>
+        </is>
+      </c>
       <c r="D160" s="3" t="inlineStr"/>
       <c r="E160" s="3" t="inlineStr"/>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H160" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H160" s="3" t="n"/>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>пом. 05</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr"/>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>10. Кабельные изделия (см. кабельный журнал ПТ.КЖ)</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="n"/>
-      <c r="D161" s="3" t="n"/>
-      <c r="E161" s="3" t="n"/>
-      <c r="F161" s="3" t="n"/>
-      <c r="G161" s="3" t="n"/>
+      <c r="A161" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Узел крепления трубы Ду80 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>узел 4, тип 3</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr"/>
+      <c r="E161" s="3" t="inlineStr"/>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>32</v>
+      </c>
       <c r="H161" s="3" t="n"/>
-      <c r="I161" s="3" t="n"/>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 5×10</t>
+          <t>Узел крепления трубы Ду100 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>узел 4, тип 3</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr"/>
       <c r="E162" s="3" t="inlineStr"/>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G162" s="3" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>с запасом 10 %</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 5×2,5</t>
+          <t>Узел крепления трубы Ду150 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>узел 4, тип 3</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr"/>
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>с запасом 10 %</t>
+          <t>количество узлов в сборе</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>Кабель ВВГнг(А)-FRLS 3×1,5</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr"/>
-      <c r="E164" s="3" t="inlineStr"/>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="n">
-        <v>25</v>
-      </c>
+      <c r="A164" s="3" t="inlineStr"/>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>7а. Изделия и материалы (системы В2, В21, В22)</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n"/>
+      <c r="D164" s="3" t="n"/>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="3" t="n"/>
       <c r="H164" s="3" t="n"/>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 4×10</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду25</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr"/>
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H165" s="3" t="n"/>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 4×1,5</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду32</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr"/>
       <c r="E166" s="3" t="inlineStr"/>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G166" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H166" s="3" t="n"/>
-      <c r="I166" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду40</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr"/>
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H167" s="3" t="n"/>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду50</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr"/>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G168" s="3" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H168" s="3" t="n"/>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду80</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr"/>
       <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>804</v>
+        <v>1</v>
       </c>
       <c r="H169" s="3" t="n"/>
-      <c r="I169" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСЭнг(А)-FRLS 1×2×0,75</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду100</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>КПСЭнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr"/>
       <c r="E170" s="3" t="inlineStr"/>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G170" s="3" t="n">
-        <v>176</v>
+        <v>6</v>
       </c>
       <c r="H170" s="3" t="n"/>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Труба гофрированная ПВХ безгалогенная Ø20 мм с протяжкой</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr"/>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду125</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 2</t>
+        </is>
+      </c>
       <c r="D171" s="3" t="inlineStr"/>
       <c r="E171" s="3" t="inlineStr"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="H171" s="3" t="n"/>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>опуски к приборам</t>
-        </is>
-      </c>
+      <c r="I171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Металлорукав в ПВХ изоляции Ø25 мм</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr"/>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду150</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 2</t>
+        </is>
+      </c>
       <c r="D172" s="3" t="inlineStr"/>
       <c r="E172" s="3" t="inlineStr"/>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G172" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H172" s="3" t="n"/>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>подключение электродвигателей</t>
-        </is>
-      </c>
+      <c r="I172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Лоток кабельный перфорированный 100×50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr"/>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду80</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 3</t>
+        </is>
+      </c>
       <c r="D173" s="3" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr"/>
       <c r="F173" s="3" t="inlineStr">
         <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H173" s="3" t="n"/>
+      <c r="I173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду100</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 3</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr"/>
+      <c r="E174" s="3" t="inlineStr"/>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду150</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 3</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr"/>
+      <c r="E175" s="3" t="inlineStr"/>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Состав огнезащитный терморасширяющийся (герметик) для заделки зазоров в гильзах, EI не ниже предела огнестойкости преграды</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr"/>
+      <c r="D176" s="3" t="inlineStr"/>
+      <c r="E176" s="3" t="inlineStr"/>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="H176" s="3" t="n"/>
+      <c r="I176" s="3" t="inlineStr">
+        <is>
+          <t>0,25 кг на проход</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Грунтовка ГФ-021 (1 слой)</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 25129-2020</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr"/>
+      <c r="E177" s="3" t="inlineStr"/>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>S=695 м²</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Эмаль ПФ-115 красная (2 слоя)</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 6465-76</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr"/>
+      <c r="E178" s="3" t="inlineStr"/>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr"/>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>8. Автоматическая установка порошкового пожаротушения помещения ВРУ (пом. 06)</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n"/>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="3" t="n"/>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="3" t="n"/>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Модуль порошкового пожаротушения закачного типа, масса ОТВ 8 кг, защищаемый объём (класс В) не менее 32 м³, электропуск</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>МПП(Н)-8 (типа «Буран-8» или аналог), ГОСТ Р 53286-2009</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr"/>
+      <c r="E180" s="3" t="inlineStr"/>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Запас модулей порошкового пожаротушения (100 %)</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>то же</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr"/>
+      <c r="E181" s="3" t="inlineStr"/>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>хранение на объекте</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Блок управления пожаротушением на одно направление</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>С2000-АСПТ</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr"/>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>у входа в пом. 06</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Извещатель пожарный дымовой оптико-электронный адресно-аналоговый</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>ДИП-34А-04</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr"/>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H183" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>пуск по 2 из 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Устройство дистанционного пуска «Пуск порошка» (жёлтое, с защитной крышкой)</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>ЭДУ 513-3АМ исп. 01</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr"/>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I184" s="3" t="inlineStr">
+        <is>
+          <t>у входа</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Табло световое «ПОРОШОК! УХОДИ!» 24 В</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Молния-24</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr"/>
+      <c r="E185" s="3" t="inlineStr"/>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>внутри</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Табло световое «ПОРОШОК! НЕ ВХОДИ!» 24 В</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Молния-24</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr"/>
+      <c r="E186" s="3" t="inlineStr"/>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I186" s="3" t="inlineStr">
+        <is>
+          <t>над дверью снаружи</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Табло световое «АВТОМАТИКА ОТКЛЮЧЕНА» 24 В</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Молния-24</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr"/>
+      <c r="E187" s="3" t="inlineStr"/>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>снаружи</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Оповещатель звуковой 24 В, 105 дБ</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Маяк-24-3М</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr"/>
+      <c r="E188" s="3" t="inlineStr"/>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t>внутри</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Извещатель магнитоконтактный (контроль закрытия двери)</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>ИО 102-26 «Аякс»</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr"/>
+      <c r="E189" s="3" t="inlineStr"/>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I189" s="3" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2×12 В 17 А·ч</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>РИП-24 исп. 01</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr"/>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I190" s="3" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Коробка коммутационная огнестойкая (Е90)</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>КМ-О (4к)-IP41</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr"/>
+      <c r="E191" s="3" t="inlineStr"/>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I191" s="3" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr"/>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>9. Автоматизация систем водяного пожаротушения</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="n"/>
+      <c r="H192" s="3" t="n"/>
+      <c r="I192" s="3" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Прибор управления насосной станцией пожаротушения (основной, резервный, жокей-насос)</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Поток-3Н</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr"/>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>насосная</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Шкаф контрольно-пусковой для электродвигателя до 30 кВт, 380 В</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>ШКП-30</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr"/>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H194" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I194" s="3" t="inlineStr">
+        <is>
+          <t>Н1, Н2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Шкаф контрольно-пусковой для электродвигателя до 4 кВт, 380 В</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>ШКП-4</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr"/>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I195" s="3" t="inlineStr">
+        <is>
+          <t>Н3</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Контроллер двухпроводной линии связи (адресные устройства ПТ)</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>С2000-КДЛ-2И</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr"/>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I196" s="3" t="inlineStr">
+        <is>
+          <t>RS-485 к ППКУП «Сириус» (пом. 03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Адресный расширитель на 2 входа (контроль затворов, дверей шкафов ПК, кнопок «Пуск насосов», аварийного уровня в приямке)</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>С2000-АР2 исп. 02</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr"/>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="H197" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I197" s="3" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2×12 В 17 А·ч</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>РИП-24 исп. 01</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr"/>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I198" s="3" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>Шкаф монтажный навесной 600×600×250 IP54 для приборов автоматики ПТ</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr"/>
+      <c r="D199" s="3" t="inlineStr"/>
+      <c r="E199" s="3" t="inlineStr"/>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>насосная</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr"/>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>10. Кабельные изделия (см. кабельный журнал ПТ.КЖ)</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n"/>
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
+      <c r="F200" s="3" t="n"/>
+      <c r="G200" s="3" t="n"/>
+      <c r="H200" s="3" t="n"/>
+      <c r="I200" s="3" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Кабель ВВГнг(А)-FRLS 5×6</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr"/>
+      <c r="E201" s="3" t="inlineStr"/>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G173" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H173" s="3" t="n"/>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>пом. 05 – пом. 06</t>
+      <c r="G201" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="H201" s="3" t="n"/>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Кабель ВВГнг(А)-FRLS 5×2,5</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr"/>
+      <c r="E202" s="3" t="inlineStr"/>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="H202" s="3" t="n"/>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Кабель ВВГнг(А)-FRLS 3×1,5</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr"/>
+      <c r="E203" s="3" t="inlineStr"/>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H203" s="3" t="n"/>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Кабель ВВГнг(А)-FRLS 4×6</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr"/>
+      <c r="E204" s="3" t="inlineStr"/>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H204" s="3" t="n"/>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Кабель ВВГнг(А)-FRLS 4×1,5</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr"/>
+      <c r="E205" s="3" t="inlineStr"/>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H205" s="3" t="n"/>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Кабель КПСнг(А)-FRLS 2×2×0,75</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr"/>
+      <c r="E206" s="3" t="inlineStr"/>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H206" s="3" t="n"/>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>Кабель КПСнг(А)-FRLS 1×2×1,5</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr"/>
+      <c r="E207" s="3" t="inlineStr"/>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H207" s="3" t="n"/>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Кабель КПСнг(А)-FRLS 1×2×0,75</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr"/>
+      <c r="E208" s="3" t="inlineStr"/>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>832</v>
+      </c>
+      <c r="H208" s="3" t="n"/>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Кабель КПСЭнг(А)-FRLS 1×2×0,75</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>КПСЭнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr"/>
+      <c r="E209" s="3" t="inlineStr"/>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="H209" s="3" t="n"/>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Труба гофрированная ПВХ безгалогенная Ø20 мм с протяжкой</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr"/>
+      <c r="D210" s="3" t="inlineStr"/>
+      <c r="E210" s="3" t="inlineStr"/>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H210" s="3" t="n"/>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>опуски к приборам</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>Металлорукав в ПВХ изоляции Ø25 мм</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr"/>
+      <c r="D211" s="3" t="inlineStr"/>
+      <c r="E211" s="3" t="inlineStr"/>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H211" s="3" t="n"/>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>подключение электродвигателей</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Лоток кабельный перфорированный 100×50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr"/>
+      <c r="D212" s="3" t="inlineStr"/>
+      <c r="E212" s="3" t="inlineStr"/>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H212" s="3" t="n"/>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>пом. 06 – тамбур 92 – пом. 05 – насосная</t>
         </is>
       </c>
     </row>
@@ -5501,10 +6682,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>16.4</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -5517,10 +6698,10 @@
         <v>80</v>
       </c>
       <c r="C3" t="n">
-        <v>162.9</v>
+        <v>116</v>
       </c>
       <c r="D3" t="n">
-        <v>172</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
@@ -5533,10 +6714,10 @@
         <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>224.9</v>
+        <v>214.5</v>
       </c>
       <c r="D4" t="n">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
@@ -5549,10 +6730,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>440.1</v>
+        <v>451.4</v>
       </c>
       <c r="D5" t="n">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6">
@@ -5565,10 +6746,10 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>300.2</v>
+        <v>302.7</v>
       </c>
       <c r="D6" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7">
@@ -5597,10 +6778,10 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>380.2</v>
+        <v>384.3</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -5613,10 +6794,10 @@
         <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>25.7</v>
+        <v>32.2</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -5629,7 +6810,7 @@
         <v>80</v>
       </c>
       <c r="C10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -5677,10 +6858,10 @@
         <v>150</v>
       </c>
       <c r="C13" t="n">
-        <v>184.4</v>
+        <v>186.6</v>
       </c>
       <c r="D13" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
@@ -5693,10 +6874,10 @@
         <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>480.9</v>
+        <v>481.1</v>
       </c>
       <c r="D14" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15">
@@ -5709,7 +6890,7 @@
         <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>359.9</v>
+        <v>360</v>
       </c>
       <c r="D15" t="n">
         <v>378</v>
@@ -5725,7 +6906,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="n">
-        <v>250.2</v>
+        <v>250.3</v>
       </c>
       <c r="D16" t="n">
         <v>263</v>
@@ -5741,10 +6922,10 @@
         <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>152.9</v>
+        <v>153.6</v>
       </c>
       <c r="D17" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18">
@@ -5757,10 +6938,10 @@
         <v>65</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>27.9</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -5805,10 +6986,10 @@
         <v>150</v>
       </c>
       <c r="C21" t="n">
-        <v>203.7</v>
+        <v>205.8</v>
       </c>
       <c r="D21" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -5822,7 +7003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5873,25 +7054,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ВРУ, панель АВР ПТ (пом. 06)</t>
+          <t>ВРУ, панель ППУ (пом. 06)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ШКП-30 Н1 (пом. 05)</t>
+          <t>ШКП-30 Н1 (насосная, подвал)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 5×10</t>
+          <t>ВВГнг(А)-FRLS 5×6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>I кат., от АВР (раздел ЭМ)</t>
+          <t>I кат., от ППУ с АВР (раздел ЭМ)</t>
         </is>
       </c>
     </row>
@@ -5903,25 +7084,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ВРУ, панель АВР ПТ (пом. 06)</t>
+          <t>ВРУ, панель ППУ (пом. 06)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ШКП-30 Н2 (пом. 05)</t>
+          <t>ШКП-30 Н2 (насосная, подвал)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 5×10</t>
+          <t>ВВГнг(А)-FRLS 5×6</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>I кат., от АВР (раздел ЭМ)</t>
+          <t>I кат., от ППУ с АВР (раздел ЭМ)</t>
         </is>
       </c>
     </row>
@@ -5933,12 +7114,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ВРУ, панель АВР ПТ (пом. 06)</t>
+          <t>ВРУ, панель ППУ (пом. 06)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ШКП-4 Н3 (пом. 05)</t>
+          <t>ШКП-4 Н3 (насосная, подвал)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5947,7 +7128,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -5959,12 +7140,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ВРУ, панель АВР ПТ (пом. 06)</t>
+          <t>ВРУ, панель ППУ (пом. 06)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Шкаф автоматики ПТ, РИП-24 (пом. 05)</t>
+          <t>Шкаф автоматики ПТ, РИП-24 (насосная, подвал)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5973,7 +7154,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -5985,7 +7166,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ВРУ, панель АВР ПТ (пом. 06)</t>
+          <t>ВРУ, панель ППУ (пом. 06)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6011,27 +7192,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ШКП-30 Н1</t>
+          <t>ВРУ, панель ППУ (пом. 06)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Электродвигатель Н1, 22 кВт</t>
+          <t>Шкаф управления дренажными насосами ШУД (насосная, подвал)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 4×10</t>
+          <t>ВВГнг(А)-FRLS 5×2,5</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>в металлорукаве</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6041,21 +7218,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ШКП-30 Н2</t>
+          <t>ШКП-30 Н1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Электродвигатель Н2, 22 кВт</t>
+          <t>Электродвигатель Н1, 15 кВт</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 4×10</t>
+          <t>ВВГнг(А)-FRLS 4×6</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -6071,17 +7248,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ШКП-4 Н3</t>
+          <t>ШКП-30 Н2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Электродвигатель Н3, 0,75 кВт</t>
+          <t>Электродвигатель Н2, 15 кВт</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 4×1,5</t>
+          <t>ВВГнг(А)-FRLS 4×6</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -6101,23 +7278,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Поток-3Н</t>
+          <t>ШКП-4 Н3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ШКП-30 Н1 (пуск, контроль)</t>
+          <t>Электродвигатель Н3, 0,55 кВт</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>ВВГнг(А)-FRLS 4×1,5</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>в металлорукаве</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6127,23 +7308,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Поток-3Н</t>
+          <t>ШУД</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ШКП-30 Н2 (пуск, контроль)</t>
+          <t>Дренажные насосы ДН1, ДН2, 0,75 кВт</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>ВВГнг(А)-FRLS 4×1,5</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>в приямке, 2 линии</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6153,12 +7338,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Поток-3Н</t>
+          <t>ШУД</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ШКП-4 Н3 (пуск, контроль)</t>
+          <t>Поплавковые выключатели приямка (3 шт.)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6167,7 +7352,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="inlineStr"/>
     </row>
@@ -6184,7 +7369,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ЭКМ-1 на напорном коллекторе</t>
+          <t>ШКП-30 Н1 (пуск, контроль)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6210,7 +7395,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ЭКМ-2 на напорном коллекторе</t>
+          <t>ШКП-30 Н2 (пуск, контроль)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6236,7 +7421,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>СДУ-М-1, СДУ-М-2 (коллектор)</t>
+          <t>ШКП-4 Н3 (пуск, контроль)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6245,7 +7430,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" t="inlineStr"/>
     </row>
@@ -6262,7 +7447,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>СДУ УУ-1, СДУ УУ-2</t>
+          <t>ЭКМ-1 на напорном коллекторе</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6271,7 +7456,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr"/>
     </row>
@@ -6283,21 +7468,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>РИП-24 (шкаф автоматики)</t>
+          <t>Поток-3Н</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Поток-3Н, С2000-КДЛ-2И</t>
+          <t>ЭКМ-2 на напорном коллекторе</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>КПСнг(А)-FRLS 2×2×0,75</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr"/>
     </row>
@@ -6309,27 +7494,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>С2000-КДЛ-2И</t>
+          <t>Поток-3Н</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Кольцевая ДПЛС: С2000-АР2 шкафов ПК (30 шт.), затворов (6 шт.)</t>
+          <t>СДУ-М-1, СДУ-М-2 (коллектор)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2×2×0,75</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>620</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>подвал, 1 и 2 этажи, кольцо</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6339,21 +7520,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>С2000-АР2 затворов (пом. 05)</t>
+          <t>Поток-3Н</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Концевые выключатели затворов (11 шт.)</t>
+          <t>СДУ УУ-1, СДУ УУ-2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2×2×0,75</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr"/>
     </row>
@@ -6365,27 +7546,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>С2000-КДЛ-2И, Поток-3Н</t>
+          <t>РИП-24 (шкаф автоматики)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ППКУП «Сириус» (место — по разделу СПС)</t>
+          <t>Поток-3Н, С2000-КДЛ-2И</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>КПСЭнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1×2×1,5</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>RS-485</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6395,25 +7572,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>С2000-АСПТ (пом. 06)</t>
+          <t>С2000-КДЛ-2И</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ППКУП «Сириус»</t>
+          <t>Кольцевая ДПЛС: С2000-АР2 шкафов ПК (30 шт.), затворов и ШУД (7 шт.)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>КПСЭнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1×2×0,75</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>640</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RS-485</t>
+          <t>подвал, 1 и 2 этажи, кольцо</t>
         </is>
       </c>
     </row>
@@ -6425,21 +7602,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>РИП-24 АУПП</t>
+          <t>С2000-АР2 затворов (насосная)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>С2000-АСПТ</t>
+          <t>Концевые выключатели затворов (12 шт.), сигналы ШУД</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>КПСнг(А)-FRLS 1×2×0,75</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F22" t="inlineStr"/>
     </row>
@@ -6451,23 +7628,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>С2000-АСПТ</t>
+          <t>С2000-КДЛ-2И, Поток-3Н</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>МПП-1...МПП-4 (цепь пуска)</t>
+          <t>ППКУП «Сириус», пом. 03 (раздел ПБ43 АПСиСОУЭ)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>КПСЭнг(А)-FRLS 1×2×0,75</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>RS-485</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6477,23 +7658,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>С2000-АСПТ</t>
+          <t>С2000-АСПТ (пом. 06)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Табло «ПОРОШОК! УХОДИ!», оповещатель</t>
+          <t>ППКУП «Сириус», пом. 03</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСЭнг(А)-FRLS 1×2×0,75</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>125</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RS-485</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6503,21 +7688,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>РИП-24 АУПП</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>С2000-АСПТ</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Табло «ПОРОШОК! НЕ ВХОДИ!», «АВТОМАТИКА ОТКЛЮЧЕНА»</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1×2×1,5</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr"/>
     </row>
@@ -6534,16 +7719,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ЭДУ «Пуск порошка», ИО 102-26 (дверь)</t>
+          <t>МПП-1...МПП-4 (цепь пуска)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1×2×1,5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F26" t="inlineStr"/>
     </row>
@@ -6555,23 +7740,101 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>С2000-АСПТ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Табло «ПОРОШОК! УХОДИ!», оповещатель</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>16</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ПТ-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>С2000-АСПТ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Табло «ПОРОШОК! НЕ ВХОДИ!», «АВТОМАТИКА ОТКЛЮЧЕНА»</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ПТ-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>С2000-АСПТ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ЭДУ «Пуск порошка», ИО 102-26 (дверь)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ПТ-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>С2000-КДЛ-2И (ответвление ДПЛС)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>ДИП-34А-04 (3 шт.) в пом. 06</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>КПСнг(А)-FRLS 1×2×0,75</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E30" t="n">
         <v>30</v>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
+++ b/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
@@ -515,7 +515,7 @@
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1. Насосная станция пожаротушения (технический подвал, оси 1–2/Д–Е)</t>
+          <t>1. Насосная станция пожаротушения (технический подвал, оси 1–3/Д–Е)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>4.88</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>6.26</v>
@@ -5556,12 +5556,12 @@
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H177" s="3" t="n"/>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>S=695 м²</t>
+          <t>S=692 м²</t>
         </is>
       </c>
     </row>
@@ -6922,10 +6922,10 @@
         <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>153.6</v>
+        <v>152.8</v>
       </c>
       <c r="D17" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18">
@@ -6938,10 +6938,10 @@
         <v>65</v>
       </c>
       <c r="C18" t="n">
-        <v>27.9</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">

--- a/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
+++ b/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
@@ -825,12 +825,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной эксцентрический приварной 159×4,5–133×4</t>
+          <t>Переход стальной эксцентрический приварной 159х4,5–133х4</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ПЭ 159×4,5-133×4, ГОСТ 17378-2001</t>
+          <t>ПЭ 159х4,5-133х4, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -858,12 +858,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический приварной 159×4,5–133×4</t>
+          <t>Переход стальной концентрический приварной 159х4,5–133х4</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ПК 159×4,5-133×4, ГОСТ 17378-2001</t>
+          <t>ПК 159х4,5-133х4, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Решётка стальная оцинкованная съёмная для приямка 1000×1000, ячейка 30×30, нагрузка 3 кН/м²</t>
+          <t>Решётка стальная оцинкованная съёмная для приямка 1000х1000, ячейка 30х30, нагрузка 3 кН/м²</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 219×6,0</t>
+          <t>Труба стальная электросварная прямошовная 219х6,0</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>219×6,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>219х6,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 159×4,5</t>
+          <t>Труба стальная электросварная прямошовная 159х4,5</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133×4,0</t>
+          <t>Труба стальная электросварная прямошовная 133х4,0</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108×4,0</t>
+          <t>Труба стальная электросварная прямошовная 108х4,0</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>60×3,5, ГОСТ 3262-75</t>
+          <t>60х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>48×3,5, ГОСТ 3262-75</t>
+          <t>48х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>42,3×3,2, ГОСТ 3262-75</t>
+          <t>42,3х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 219×6,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 219х6,0</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 108×4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 219×6,0 с ответвлением 159×4,5</t>
+          <t>Тройник стальной приварной 219х6,0 с ответвлением 159х4,5</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 219×6,0 с ответвлением 108×4,0</t>
+          <t>Тройник стальной приварной 219х6,0 с ответвлением 108х4,0</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Заглушка стальная эллиптическая 219×6,0</t>
+          <t>Заглушка стальная эллиптическая 219х6,0</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду25×3,2</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду25х3,2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>33,5×3,2, ГОСТ 3262-75</t>
+          <t>33,5х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>42,3×3,2, ГОСТ 3262-75</t>
+          <t>42,3х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>48×3,5, ГОСТ 3262-75</t>
+          <t>48х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>60×3,5, ГОСТ 3262-75</t>
+          <t>60х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76×3,5</t>
+          <t>Труба стальная электросварная прямошовная 76х3,5</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
@@ -2345,12 +2345,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89×3,5</t>
+          <t>Труба стальная электросварная прямошовная 89х3,5</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108×4,0</t>
+          <t>Труба стальная электросварная прямошовная 108х4,0</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133×4,0</t>
+          <t>Труба стальная электросварная прямошовная 133х4,0</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 159×4,5</t>
+          <t>Труба стальная электросварная прямошовная 159х4,5</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной Ду50×Ду32 (сварной/резьбовой)</t>
+          <t>Тройник стальной Ду50хДу32 (сварной/резьбовой)</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76×3,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 76х3,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 89×3,5 с ответвлением 33,5×3,2 (врезка)</t>
+          <t>Тройник стальной приварной 89х3,5 с ответвлением 33,5х3,2 (врезка)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 89×3,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 89х3,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108×4,0 с ответвлением 60×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133×4,0 с ответвлением 60×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 133х4,0 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133×4,0 с ответвлением 76×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 133х4,0 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 42,3×3,2 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 42,3х3,2 (врезка)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 76×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 133×4,0 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 133х4,0 (врезка)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5</t>
+          <t>Тройник стальной приварной 159х4,5</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 33,5×3,2</t>
+          <t>Отвод стальной крутоизогнутый 90° 33,5х3,2</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 42,3×3,2</t>
+          <t>Отвод стальной крутоизогнутый 90° 42,3х3,2</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 60×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 60х3,5</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 76×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 76х3,5</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 133×4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 133х4,0</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 42,3×3,2–33,5×3,2</t>
+          <t>Переход стальной концентрический 42,3х3,2–33,5х3,2</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 48×3,5–42,3×3,2</t>
+          <t>Переход стальной концентрический 48х3,5–42,3х3,2</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60×3,5–42,3×3,2</t>
+          <t>Переход стальной концентрический 60х3,5–42,3х3,2</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60×3,5–48×3,5</t>
+          <t>Переход стальной концентрический 60х3,5–48х3,5</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 76×3,5–60×3,5</t>
+          <t>Переход стальной концентрический 76х3,5–60х3,5</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
+          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 108×4,0–76×3,5</t>
+          <t>Переход стальной концентрический 108х4,0–76х3,5</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133×4,0–89×3,5</t>
+          <t>Переход стальной концентрический 133х4,0–89х3,5</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133×4,0–108×4,0</t>
+          <t>Переход стальной концентрический 133х4,0–108х4,0</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 159×4,5–133×4,0</t>
+          <t>Переход стальной концентрический 159х4,5–133х4,0</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду25×3,2</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду25х3,2</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>33,5×3,2, ГОСТ 3262-75</t>
+          <t>33,5х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32×3,2</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>42,3×3,2, ГОСТ 3262-75</t>
+          <t>42,3х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
@@ -3314,12 +3314,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>48×3,5, ГОСТ 3262-75</t>
+          <t>48х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50×3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>60×3,5, ГОСТ 3262-75</t>
+          <t>60х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76×3,5</t>
+          <t>Труба стальная электросварная прямошовная 76х3,5</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89×3,5</t>
+          <t>Труба стальная электросварная прямошовная 89х3,5</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133×4,0</t>
+          <t>Труба стальная электросварная прямошовная 133х4,0</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>133×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 159×4,5</t>
+          <t>Труба стальная электросварная прямошовная 159х4,5</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>159×4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76×3,5 с ответвлением 42,3×3,2 (врезка)</t>
+          <t>Тройник стальной приварной 76х3,5 с ответвлением 42,3х3,2 (врезка)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76×3,5 с ответвлением 48×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 76х3,5 с ответвлением 48х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133×4,0 с ответвлением 76×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 133х4,0 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 60×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 76×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5 с ответвлением 89×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 89х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159×4,5</t>
+          <t>Тройник стальной приварной 159х4,5</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 33,5×3,2</t>
+          <t>Отвод стальной крутоизогнутый 90° 33,5х3,2</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 60×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 60х3,5</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 89×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159×4,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 42,3×3,2–33,5×3,2</t>
+          <t>Переход стальной концентрический 42,3х3,2–33,5х3,2</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 48×3,5–42,3×3,2</t>
+          <t>Переход стальной концентрический 48х3,5–42,3х3,2</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60×3,5–48×3,5</t>
+          <t>Переход стальной концентрический 60х3,5–48х3,5</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 76×3,5–60×3,5</t>
+          <t>Переход стальной концентрический 76х3,5–60х3,5</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
+          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133×4,0–89×3,5</t>
+          <t>Переход стальной концентрический 133х4,0–89х3,5</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 159×4,5–133×4,0</t>
+          <t>Переход стальной концентрический 159х4,5–133х4,0</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76×3,5</t>
+          <t>Труба стальная электросварная прямошовная 76х3,5</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>76×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr"/>
@@ -4276,12 +4276,12 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89×3,5</t>
+          <t>Труба стальная электросварная прямошовная 89х3,5</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>89×3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr"/>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108×4,0</t>
+          <t>Труба стальная электросварная прямошовная 108х4,0</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>108×4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108×4,0 с ответвлением 76×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108×4,0 с ответвлением 89×3,5 (врезка)</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 89х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108×4,0</t>
+          <t>Тройник стальной приварной 108х4,0</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 89×3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 108×4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89×3,5–76×3,5</t>
+          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2×12 В 17 А·ч</t>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2×12 В 17 А·ч</t>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Шкаф монтажный навесной 600×600×250 IP54 для приборов автоматики ПТ</t>
+          <t>Шкаф монтажный навесной 600х600х250 IP54 для приборов автоматики ПТ</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr"/>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 5×6</t>
+          <t>Кабель ВВГнг(А)-FRLS 5х6</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 5×2,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 5х2,5</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 3×1,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 3х1,5</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 4×6</t>
+          <t>Кабель ВВГнг(А)-FRLS 4х6</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 4×1,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 4х1,5</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>Кабель КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>Кабель КПСнг(А)-FRLS 1х2х1,5</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>Кабель КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСЭнг(А)-FRLS 1×2×0,75</t>
+          <t>Кабель КПСЭнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Лоток кабельный перфорированный 100×50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
+          <t>Лоток кабельный перфорированный 100х50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr"/>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 5×6</t>
+          <t>ВВГнг(А)-FRLS 5х6</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 5×6</t>
+          <t>ВВГнг(А)-FRLS 5х6</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 5×2,5</t>
+          <t>ВВГнг(А)-FRLS 5х2,5</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 3×1,5</t>
+          <t>ВВГнг(А)-FRLS 3х1,5</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 3×1,5</t>
+          <t>ВВГнг(А)-FRLS 3х1,5</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 5×2,5</t>
+          <t>ВВГнг(А)-FRLS 5х2,5</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 4×6</t>
+          <t>ВВГнг(А)-FRLS 4х6</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 4×6</t>
+          <t>ВВГнг(А)-FRLS 4х6</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 4×1,5</t>
+          <t>ВВГнг(А)-FRLS 4х1,5</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS 4×1,5</t>
+          <t>ВВГнг(А)-FRLS 4х1,5</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 2×2×0,75</t>
+          <t>КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>КПСнг(А)-FRLS 1х2х1,5</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>КПСЭнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСЭнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>КПСЭнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСЭнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>КПСнг(А)-FRLS 1х2х1,5</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×1,5</t>
+          <t>КПСнг(А)-FRLS 1х2х1,5</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS 1×2×0,75</t>
+          <t>КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="E30" t="n">

--- a/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
+++ b/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I212"/>
+  <dimension ref="A1:I216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Насос центробежный вертикальный (in-line) для систем пожаротушения, Q=145 м³/ч, H=21 м, N=15 кВт, 380 В, 2900 об/мин, фланцы Ду125 PN16 (Н1 — рабочий, Н2 — резервный)</t>
+          <t>Насос центробежный вертикальный (in-line) для систем пожаротушения, Q=145 м³/ч, H=22 м, N=15 кВт, 380 В, 2900 об/мин, фланцы Ду125 PN16 (Н1 — рабочий, Н2 — резервный)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Клапан обратный межфланцевый двухстворчатый Ду100 PN16</t>
+          <t>Фильтр сетчатый фланцевый Ду150 PN16 (перед регулятором давления)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду150</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
@@ -775,14 +775,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>патрубки ГМ-80</t>
+          <t>вводы 1, 2</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Компенсатор резиновый фланцевый (виброкомпенсатор) Ду125 PN16</t>
+          <t>Клапан редукционный (регулятор давления «после себя») фланцевый Ду150 PN16, диапазон настройки 0,1–0,6 МПа, настройка 0,20 МПа, Kv не менее 350 м³/ч</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>по опросному листу</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -808,14 +808,14 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Н1, Н2</t>
+          <t>вводы 1, 2</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной эксцентрический приварной 159х4,5–133х4</t>
+          <t>Клапан обратный межфланцевый двухстворчатый Ду100 PN16</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ПЭ 159х4,5-133х4, ГОСТ 17378-2001</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -841,14 +841,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>всасывание</t>
+          <t>патрубки ГМ-80</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический приварной 159х4,5–133х4</t>
+          <t>Компенсатор резиновый фланцевый (виброкомпенсатор) Ду125 PN16</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ПК 159х4,5-133х4, ГОСТ 17378-2001</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr"/>
@@ -874,14 +874,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>нагнетание</t>
+          <t>Н1, Н2</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Кран шаровой латунный муфтовый Ду32 PN16</t>
+          <t>Переход стальной эксцентрический приварной 159х4,5–133х4</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>ПЭ 159х4,5-133х4, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -907,14 +907,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>обвязка Н3, бак</t>
+          <t>всасывание</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный муфтовый Ду32 PN16</t>
+          <t>Переход стальной концентрический приварной 159х4,5–133х4</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>ПК 159х4,5-133х4, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -940,12 +940,16 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>нагнетание</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -953,12 +957,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Манометр показывающий МП-100, 0–1,6 МПа, кл. 1,5, с краном трёхходовым 11Б18бк</t>
+          <t>Кран шаровой латунный муфтовый Ду32 PN16</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>МП-100, ГОСТ 2405-88</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -969,14 +973,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>вводы, Н1–Н3, коллекторы</t>
+          <t>обвязка Н3, бак</t>
         </is>
       </c>
     </row>
@@ -986,12 +990,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Манометр электроконтактный 0–1,6 МПа, кл. 1,5 (управление Н3 и пуск Н1/Н2)</t>
+          <t>Клапан обратный пружинный муфтовый Ду32 PN16</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>ДМ2005Сг1Ex, ГОСТ 2405-88</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -1002,10 +1006,10 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
     </row>
@@ -1015,34 +1019,30 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Сигнализатор давления универсальный (пуск основного насоса по падению давления)</t>
+          <t>Манометр показывающий МП-100, 0–1,6 МПа, кл. 1,5, с краном трёхходовым 11Б18бк</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>СДУ-М</t>
+          <t>МП-100, ГОСТ 2405-88</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>ПО «Спецавтоматика» или аналог</t>
-        </is>
-      </c>
+      <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>коллектор</t>
+          <t>вводы до и после регуляторов, Н1–Н3, коллекторы</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Расходомер-счётчик ультразвуковой накладной Ду100 (линия опробования насосов)</t>
+          <t>Манометр электроконтактный 0–1,6 МПа, кл. 1,5 (управление Н3 и пуск Н1/Н2)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>ДМ2005Сг1Ex, ГОСТ 2405-88</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
     </row>
@@ -1081,30 +1081,34 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Патрубок для подключения передвижной пожарной техники: головка соединительная муфтовая ГМ-80 с заглушкой ГЗ-80</t>
+          <t>Сигнализатор давления универсальный (пуск основного насоса по падению давления)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>ГМ-80, ГЗ-80, ГОСТ Р 53279-2009</t>
+          <t>СДУ-М</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ПО «Спецавтоматика» или аналог</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>на фасаде у оси 1</t>
+          <t>коллектор</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1118,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Кран шаровой стальной муфтовый Ду50 PN16 (дренаж/опорожнение)</t>
+          <t>Расходомер-счётчик ультразвуковой накладной Ду100 (линия опробования насосов)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -1130,10 +1134,10 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
     </row>
@@ -1143,26 +1147,32 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Знак пожарной безопасности «Патрубок подключения пожарной техники» (фотолюминесцентный)</t>
+          <t>Патрубок для подключения передвижной пожарной техники: головка соединительная муфтовая ГМ-80 с заглушкой ГЗ-80</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>F 08/по ГОСТ 12.4.026, ГОСТ 12.4.026-2015</t>
+          <t>ГМ-80, ГЗ-80, ГОСТ Р 53279-2009</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>на фасаде у оси 1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1170,12 +1180,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Насос дренажный погружной для чистой и слабозагрязнённой воды, Q=10 м³/ч, H=10 м, N=0,75 кВт, 380 В, с поплавковым выключателем (ДН1 — рабочий, ДН2 — резервный)</t>
+          <t>Кран шаровой стальной муфтовый Ду50 PN16 (дренаж/опорожнение)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>по опросному листу; аналог — «Гном 10-10»</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -1186,14 +1196,14 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>16</v>
+        <v>1.6</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>приямок насосной</t>
+          <t>дренаж УУ, точка подключения ВК</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1213,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Шкаф управления дренажными насосами: поочерёдная работа, включение резервного, сигнал «Аварийный уровень» (сухой контакт)</t>
+          <t>Знак пожарной безопасности «Патрубок подключения пожарной техники» (фотолюминесцентный)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>по опросному листу</t>
+          <t>F 08/по ГОСТ 12.4.026, ГОСТ 12.4.026-2015</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
@@ -1221,14 +1231,8 @@
       <c r="G26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>насосная</t>
-        </is>
-      </c>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1236,10 +1240,14 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Выключатель поплавковый (уровни «пуск», «стоп», «аварийный»)</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
+          <t>Насос дренажный погружной для чистой и слабозагрязнённой воды, Q=10 м³/ч, H=10 м, N=0,75 кВт, 380 В, с поплавковым выключателем (ДН1 — рабочий, ДН2 — резервный)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>по опросному листу; аналог — «Гном 10-10»</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
@@ -1248,14 +1256,14 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.4</v>
+        <v>16</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>приямок</t>
+          <t>приямок насосной</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1273,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный муфтовый Ду40 PN16</t>
+          <t>Шкаф управления дренажными насосами: поочерёдная работа, включение резервного, сигнал «Аварийный уровень» (сухой контакт)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>по опросному листу</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -1281,14 +1289,14 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>ДН1, ДН2</t>
+          <t>насосная</t>
         </is>
       </c>
     </row>
@@ -1298,14 +1306,10 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Кран шаровой стальной муфтовый Ду40 PN16</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Ду40</t>
-        </is>
-      </c>
+          <t>Выключатель поплавковый (уровни «пуск», «стоп», «аварийный»)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
@@ -1317,11 +1321,11 @@
         <v>3</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>ДН1, ДН2, выпуск</t>
+          <t>приямок</t>
         </is>
       </c>
     </row>
@@ -1331,10 +1335,14 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Решётка стальная оцинкованная съёмная для приямка 1000х1000, ячейка 30х30, нагрузка 3 кН/м²</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr"/>
+          <t>Клапан обратный пружинный муфтовый Ду40 PN16</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Ду40</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr"/>
       <c r="E30" s="3" t="inlineStr"/>
       <c r="F30" s="3" t="inlineStr">
@@ -1343,14 +1351,14 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>32</v>
+        <v>0.7</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>ДН1, ДН2</t>
         </is>
       </c>
     </row>
@@ -1360,10 +1368,14 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Виброизолятор резинометаллический под раму насоса</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
+          <t>Кран шаровой стальной муфтовый Ду40 PN16</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Ду40</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
@@ -1372,97 +1384,89 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>4 на насос</t>
+          <t>ДН1, ДН2</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>1а. Трубопроводы и фасонные части обвязки насосной</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Решётка стальная оцинкованная съёмная для приямка 1000х1000, ячейка 30х30, нагрузка 3 кН/м²</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 219х6,0</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>219х6,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
-        </is>
-      </c>
+          <t>Виброизолятор резинометаллический под раму насоса</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>31.52</v>
+        <v>0.5</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>всасывающий и напорный коллекторы</t>
+          <t>4 на насос</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Труба стальная электросварная прямошовная 159х4,5</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>вводы, линии Н1, Н2, обвод, УУ</t>
-        </is>
-      </c>
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>1а. Трубопроводы и фасонные части обвязки насосной</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1470,12 +1474,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133х4,0</t>
+          <t>Труба стальная электросварная прямошовная 219х6,0</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>219х6,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
@@ -1486,14 +1490,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>12.73</v>
+        <v>31.52</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>у насосов</t>
+          <t>всасывающий и напорный коллекторы</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1507,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108х4,0</t>
+          <t>Труба стальная электросварная прямошовная 159х4,5</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1519,14 +1523,14 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>10.26</v>
+        <v>17.15</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>опробование, линия к ГМ-80</t>
+          <t>вводы, линии Н1, Н2, обвод, УУ</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1540,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
+          <t>Труба стальная электросварная прямошовная 133х4,0</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>60х3,5, ГОСТ 3262-75</t>
+          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1552,14 +1556,14 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4.88</v>
+        <v>12.73</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>дренаж УУ, выпуск дренажных насосов</t>
+          <t>у насосов</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1573,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
+          <t>Труба стальная электросварная прямошовная 108х4,0</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>48х3,5, ГОСТ 3262-75</t>
+          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
@@ -1585,14 +1589,14 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>3.84</v>
+        <v>10.26</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>напорные ДН1, ДН2</t>
+          <t>опробование, линия к ГМ-80</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1606,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>42,3х3,2, ГОСТ 3262-75</t>
+          <t>60х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1618,14 +1622,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3.09</v>
+        <v>4.88</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>обвязка Н3</t>
+          <t>дренаж УУ, напорная линия ДН до точки подключения ВК</t>
         </is>
       </c>
     </row>
@@ -1635,26 +1639,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 219х6,0</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>48х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>напорные ДН1, ДН2</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -1662,26 +1672,32 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>42,3х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>обвязка Н3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -1689,7 +1705,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 219х6,0</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1705,7 +1721,7 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="inlineStr"/>
@@ -1716,12 +1732,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 219х6,0 с ответвлением 159х4,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
@@ -1732,14 +1748,10 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>врезки в коллекторы</t>
-        </is>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -1747,12 +1759,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 219х6,0 с ответвлением 108х4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1763,7 +1775,7 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -1774,12 +1786,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Заглушка стальная эллиптическая 219х6,0</t>
+          <t>Тройник стальной приварной 219х6,0 с ответвлением 159х4,5</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17379-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1790,12 +1802,12 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>торцы коллекторов</t>
+          <t>врезки в коллекторы</t>
         </is>
       </c>
     </row>
@@ -1805,30 +1817,26 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Фланец стальной плоский приварной Ду150 PN16 (комплект с крепежом и прокладками)</t>
+          <t>Тройник стальной приварной 219х6,0 с ответвлением 108х4,0</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 33259-2015</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>под арматуру</t>
-        </is>
-      </c>
+      <c r="I46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -1836,26 +1844,30 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Фланец стальной плоский приварной Ду100 PN16 (комплект с крепежом и прокладками)</t>
+          <t>Заглушка стальная эллиптическая 219х6,0</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 33259-2015</t>
+          <t>, ГОСТ 17379-2001</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>торцы коллекторов</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -1863,7 +1875,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Фланец стальной плоский приварной Ду125 PN16 (комплект с крепежом и прокладками)</t>
+          <t>Фланец стальной плоский приварной Ду150 PN16 (комплект с крепежом и прокладками)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1879,103 +1891,87 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>насосы, компенсаторы</t>
+          <t>под арматуру</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr"/>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2. Автоматическая установка водяного пожаротушения. Секция 1 — В21 (1 этаж), секция 2 — В22 (2 этаж)</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
+      <c r="A49" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Фланец стальной плоский приварной Ду100 PN16 (комплект с крепежом и прокладками)</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 33259-2015</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
+      <c r="I49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Ороситель спринклерный водяной розеткой вниз, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
+          <t>Фланец стальной плоский приварной Ду125 PN16 (комплект с крепежом и прокладками)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>СВО0-РНо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
+          <t>, ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>ПО «Спецавтоматика» или аналог</t>
-        </is>
-      </c>
+      <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>секция 1</t>
+          <t>насосы, компенсаторы</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Ороситель спринклерный водяной розеткой вверх, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>СВО0-РВо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>ПО «Спецавтоматика» или аналог</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>462</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>секция 2</t>
-        </is>
-      </c>
+      <c r="A51" s="3" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2. Автоматическая установка водяного пожаротушения. Секция 1 — В21 (1 этаж), секция 2 — В22 (2 этаж)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -1983,30 +1979,34 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Оросители запасные (10 % от смонтированных) в шкафу для хранения с ключом монтажным</t>
+          <t>Ороситель спринклерный водяной розеткой вниз, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>то же</t>
+          <t>СВО0-РНо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>ПО «Спецавтоматика» или аналог</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>97</v>
+        <v>500</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>50 РНо + 47 РВо</t>
+          <t>секция 1</t>
         </is>
       </c>
     </row>
@@ -2016,26 +2016,34 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Шкаф для хранения запасных оросителей</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr"/>
+          <t>Ороситель спринклерный водяной розеткой вверх, K=0,42 л/(с·МПа⁰·⁵), tраб=68 °C, присоединение R1/2</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>СВО0-РВо0,42-R1/2/P68.B3, ГОСТ Р 51043-2002</t>
+        </is>
+      </c>
       <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>ПО «Спецавтоматика» или аналог</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1</v>
+        <v>462</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>6</v>
+        <v>0.1</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>насосная</t>
+          <t>секция 2</t>
         </is>
       </c>
     </row>
@@ -2045,28 +2053,32 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Узел промывки и опорожнения в конце питающего трубопровода: кран шаровой Ду50, заглушка G2" с цепочкой</t>
+          <t>Оросители запасные (10 % от смонтированных) в шкафу для хранения с ключом монтажным</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>см. узел 8</t>
+          <t>то же</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>50 РНо + 47 РВо</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -2074,28 +2086,28 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Узел опробования в диктующей точке секции: кран шаровой Ду25, манометр МП-100 0–1,0 МПа, насадок K=0,42</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>см. узел 9</t>
-        </is>
-      </c>
+          <t>Шкаф для хранения запасных оросителей</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr"/>
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I55" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>насосная</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -2103,32 +2115,28 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Воздухоотводчик автоматический Ду15 PN16 с запорным краном</t>
+          <t>Узел промывки и опорожнения в конце питающего трубопровода: кран шаровой Ду50, заглушка G2" с цепочкой</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Ду15</t>
+          <t>см. узел 8</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
       <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
         <v>4</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>в верхних точках питающих</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -2136,109 +2144,105 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Бобышка (муфта) стальная приварная G1/2 для присоединения оросителя</t>
+          <t>Узел опробования в диктующей точке секции: кран шаровой Ду25, манометр МП-100 0–1,0 МПа, насадок K=0,42</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>G1/2</t>
+          <t>см. узел 9</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
       <c r="E57" s="3" t="inlineStr"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>962</v>
+        <v>2</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.08</v>
+        <v>1.5</v>
       </c>
       <c r="I57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr"/>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>3. Трубопроводы и фасонные части системы В21 (секция 1)</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
+      <c r="A58" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Воздухоотводчик автоматический Ду15 PN16 с запорным краном</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>в верхних точках питающих</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду25х3,2</t>
+          <t>Бобышка (муфта) стальная приварная G1/2 для присоединения оросителя</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>33,5х3,2, ГОСТ 3262-75</t>
+          <t>G1/2</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>474</v>
+        <v>962</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>42,3х3,2, ГОСТ 3262-75</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>318</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+      <c r="A60" s="3" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3. Трубопроводы и фасонные части системы В21 (секция 1)</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -2246,12 +2250,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду25х3,2</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>48х3,5, ГОСТ 3262-75</t>
+          <t>33,5х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -2262,10 +2266,10 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>286</v>
+        <v>474</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>3.84</v>
+        <v>2.39</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
@@ -2279,12 +2283,12 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>60х3,5, ГОСТ 3262-75</t>
+          <t>42,3х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -2295,10 +2299,10 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>404</v>
+        <v>318</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>4.88</v>
+        <v>3.09</v>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
@@ -2312,12 +2316,12 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>48х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
@@ -2328,10 +2332,10 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>34</v>
+        <v>286</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>6.26</v>
+        <v>3.84</v>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
@@ -2345,12 +2349,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>60х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
@@ -2361,10 +2365,10 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>5</v>
+        <v>404</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>7.38</v>
+        <v>4.88</v>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
@@ -2378,12 +2382,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108х4,0</t>
+          <t>Труба стальная электросварная прямошовная 76х3,5</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
@@ -2394,10 +2398,10 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>10.26</v>
+        <v>6.26</v>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
@@ -2411,12 +2415,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133х4,0</t>
+          <t>Труба стальная электросварная прямошовная 89х3,5</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
@@ -2427,10 +2431,10 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>12.73</v>
+        <v>7.38</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
@@ -2444,12 +2448,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 159х4,5</t>
+          <t>Труба стальная электросварная прямошовная 108х4,0</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
@@ -2460,10 +2464,10 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>196</v>
+        <v>5</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>17.15</v>
+        <v>10.26</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
@@ -2477,26 +2481,32 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной Ду50хДу32 (сварной/резьбовой)</t>
+          <t>Труба стальная электросварная прямошовная 133х4,0</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 8948-75 / сварка</t>
+          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr"/>
       <c r="E68" s="3" t="inlineStr"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -2504,26 +2514,32 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76х3,5 с ответвлением 60х3,5 (врезка)</t>
+          <t>Труба стальная электросварная прямошовная 159х4,5</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="3" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -2531,12 +2547,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 89х3,5 с ответвлением 33,5х3,2 (врезка)</t>
+          <t>Тройник стальной Ду50хДу32 (сварной/резьбовой)</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>, ГОСТ 8948-75 / сварка</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
@@ -2547,7 +2563,7 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="inlineStr"/>
@@ -2558,7 +2574,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 89х3,5 с ответвлением 60х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 76х3,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -2574,7 +2590,7 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="inlineStr"/>
@@ -2585,7 +2601,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108х4,0 с ответвлением 60х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 89х3,5 с ответвлением 33,5х3,2 (врезка)</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2612,7 +2628,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133х4,0 с ответвлением 60х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 89х3,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -2639,7 +2655,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133х4,0 с ответвлением 76х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2655,7 +2671,7 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="inlineStr"/>
@@ -2666,7 +2682,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5 с ответвлением 42,3х3,2 (врезка)</t>
+          <t>Тройник стальной приварной 133х4,0 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -2682,7 +2698,7 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="inlineStr"/>
@@ -2693,7 +2709,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5 с ответвлением 60х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 133х4,0 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2709,7 +2725,7 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="inlineStr"/>
@@ -2720,7 +2736,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5 с ответвлением 76х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 42,3х3,2 (врезка)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -2736,7 +2752,7 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="inlineStr"/>
@@ -2747,7 +2763,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5 с ответвлением 133х4,0 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -2763,7 +2779,7 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="inlineStr"/>
@@ -2774,7 +2790,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -2790,7 +2806,7 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="inlineStr"/>
@@ -2801,12 +2817,12 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 33,5х3,2</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 133х4,0 (врезка)</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr"/>
@@ -2817,7 +2833,7 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="inlineStr"/>
@@ -2828,12 +2844,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 42,3х3,2</t>
+          <t>Тройник стальной приварной 159х4,5</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
@@ -2844,7 +2860,7 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="inlineStr"/>
@@ -2855,7 +2871,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 60х3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 33,5х3,2</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2871,7 +2887,7 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="inlineStr"/>
@@ -2882,7 +2898,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 76х3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 42,3х3,2</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -2909,7 +2925,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 133х4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 60х3,5</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -2925,7 +2941,7 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="inlineStr"/>
@@ -2936,7 +2952,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 76х3,5</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -2952,7 +2968,7 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="inlineStr"/>
@@ -2963,12 +2979,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 42,3х3,2–33,5х3,2</t>
+          <t>Отвод стальной крутоизогнутый 90° 133х4,0</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
@@ -2979,7 +2995,7 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="inlineStr"/>
@@ -2990,12 +3006,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 48х3,5–42,3х3,2</t>
+          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
@@ -3006,7 +3022,7 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="inlineStr"/>
@@ -3017,7 +3033,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60х3,5–42,3х3,2</t>
+          <t>Переход стальной концентрический 42,3х3,2–33,5х3,2</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3033,7 +3049,7 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="inlineStr"/>
@@ -3044,7 +3060,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60х3,5–48х3,5</t>
+          <t>Переход стальной концентрический 48х3,5–42,3х3,2</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3071,7 +3087,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 76х3,5–60х3,5</t>
+          <t>Переход стальной концентрический 60х3,5–42,3х3,2</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3087,7 +3103,7 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="inlineStr"/>
@@ -3098,7 +3114,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
+          <t>Переход стальной концентрический 60х3,5–48х3,5</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3114,7 +3130,7 @@
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="inlineStr"/>
@@ -3125,7 +3141,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 108х4,0–76х3,5</t>
+          <t>Переход стальной концентрический 76х3,5–60х3,5</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3141,7 +3157,7 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="inlineStr"/>
@@ -3152,7 +3168,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133х4,0–89х3,5</t>
+          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3179,7 +3195,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133х4,0–108х4,0</t>
+          <t>Переход стальной концентрический 108х4,0–76х3,5</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3206,7 +3222,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 159х4,5–133х4,0</t>
+          <t>Переход стальной концентрический 133х4,0–89х3,5</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3222,91 +3238,79 @@
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr"/>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>4. Трубопроводы и фасонные части системы В22 (секция 2)</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="n"/>
-      <c r="G96" s="3" t="n"/>
+      <c r="A96" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Переход стальной концентрический 133х4,0–108х4,0</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17378-2001</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
+      <c r="I96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду25х3,2</t>
+          <t>Переход стальной концентрический 159х4,5–133х4,0</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>33,5х3,2, ГОСТ 3262-75</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
       <c r="E97" s="3" t="inlineStr"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>506</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>42,3х3,2, ГОСТ 3262-75</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>378</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+      <c r="A98" s="3" t="inlineStr"/>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>4. Трубопроводы и фасонные части системы В22 (секция 2)</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n"/>
+      <c r="D98" s="3" t="n"/>
+      <c r="E98" s="3" t="n"/>
+      <c r="F98" s="3" t="n"/>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -3314,12 +3318,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду25х3,2</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>48х3,5, ГОСТ 3262-75</t>
+          <t>33,5х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
@@ -3330,10 +3334,10 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>263</v>
+        <v>506</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>3.84</v>
+        <v>2.39</v>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
@@ -3347,12 +3351,12 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду32х3,2</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>60х3,5, ГОСТ 3262-75</t>
+          <t>42,3х3,2, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
@@ -3363,10 +3367,10 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>161</v>
+        <v>378</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>4.88</v>
+        <v>3.09</v>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
@@ -3380,12 +3384,12 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду40х3,5</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>48х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr"/>
@@ -3396,10 +3400,10 @@
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>14</v>
+        <v>263</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>6.26</v>
+        <v>3.84</v>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
@@ -3413,12 +3417,12 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89х3,5</t>
+          <t>Труба стальная водогазопроводная обыкновенная Ду50х3,5</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>60х3,5, ГОСТ 3262-75</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
@@ -3429,10 +3433,10 @@
         </is>
       </c>
       <c r="G102" s="3" t="n">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>7.38</v>
+        <v>4.88</v>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
@@ -3446,12 +3450,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 133х4,0</t>
+          <t>Труба стальная электросварная прямошовная 76х3,5</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr"/>
@@ -3462,10 +3466,10 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>12.73</v>
+        <v>6.26</v>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
@@ -3479,12 +3483,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 159х4,5</t>
+          <t>Труба стальная электросварная прямошовная 89х3,5</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr"/>
@@ -3495,10 +3499,10 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>217</v>
+        <v>8</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>17.15</v>
+        <v>7.38</v>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
@@ -3512,26 +3516,32 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76х3,5 с ответвлением 42,3х3,2 (врезка)</t>
+          <t>Труба стальная электросварная прямошовная 133х4,0</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>133х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -3539,26 +3549,32 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 76х3,5 с ответвлением 48х3,5 (врезка)</t>
+          <t>Труба стальная электросварная прямошовная 159х4,5</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>159х4,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr"/>
       <c r="E106" s="3" t="inlineStr"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="H106" s="3" t="n"/>
-      <c r="I106" s="3" t="inlineStr"/>
+        <v>217</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -3566,7 +3582,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 133х4,0 с ответвлением 76х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 76х3,5 с ответвлением 42,3х3,2 (врезка)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -3582,7 +3598,7 @@
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H107" s="3" t="n"/>
       <c r="I107" s="3" t="inlineStr"/>
@@ -3593,7 +3609,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5 с ответвлением 60х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 76х3,5 с ответвлением 48х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -3609,7 +3625,7 @@
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="H108" s="3" t="n"/>
       <c r="I108" s="3" t="inlineStr"/>
@@ -3620,7 +3636,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5 с ответвлением 76х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 133х4,0 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -3636,7 +3652,7 @@
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="H109" s="3" t="n"/>
       <c r="I109" s="3" t="inlineStr"/>
@@ -3647,7 +3663,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5 с ответвлением 89х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 60х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -3663,7 +3679,7 @@
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H110" s="3" t="n"/>
       <c r="I110" s="3" t="inlineStr"/>
@@ -3674,7 +3690,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 159х4,5</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -3690,7 +3706,7 @@
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="H111" s="3" t="n"/>
       <c r="I111" s="3" t="inlineStr"/>
@@ -3701,12 +3717,12 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 33,5х3,2</t>
+          <t>Тройник стальной приварной 159х4,5 с ответвлением 89х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr"/>
@@ -3717,7 +3733,7 @@
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="H112" s="3" t="n"/>
       <c r="I112" s="3" t="inlineStr"/>
@@ -3728,12 +3744,12 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 60х3,5</t>
+          <t>Тройник стальной приварной 159х4,5</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr"/>
@@ -3744,7 +3760,7 @@
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H113" s="3" t="n"/>
       <c r="I113" s="3" t="inlineStr"/>
@@ -3755,7 +3771,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 33,5х3,2</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -3771,7 +3787,7 @@
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="inlineStr"/>
@@ -3782,7 +3798,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 60х3,5</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -3798,7 +3814,7 @@
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="inlineStr"/>
@@ -3809,12 +3825,12 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 42,3х3,2–33,5х3,2</t>
+          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr"/>
@@ -3825,7 +3841,7 @@
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>140</v>
+        <v>4</v>
       </c>
       <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="inlineStr"/>
@@ -3836,12 +3852,12 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 48х3,5–42,3х3,2</t>
+          <t>Отвод стальной крутоизогнутый 90° 159х4,5</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr"/>
@@ -3852,7 +3868,7 @@
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="inlineStr"/>
@@ -3863,7 +3879,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 60х3,5–48х3,5</t>
+          <t>Переход стальной концентрический 42,3х3,2–33,5х3,2</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -3879,7 +3895,7 @@
         </is>
       </c>
       <c r="G118" s="3" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="inlineStr"/>
@@ -3890,7 +3906,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 76х3,5–60х3,5</t>
+          <t>Переход стальной концентрический 48х3,5–42,3х3,2</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -3906,7 +3922,7 @@
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="H119" s="3" t="n"/>
       <c r="I119" s="3" t="inlineStr"/>
@@ -3917,7 +3933,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
+          <t>Переход стальной концентрический 60х3,5–48х3,5</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -3933,7 +3949,7 @@
         </is>
       </c>
       <c r="G120" s="3" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="inlineStr"/>
@@ -3944,7 +3960,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 133х4,0–89х3,5</t>
+          <t>Переход стальной концентрический 76х3,5–60х3,5</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -3960,7 +3976,7 @@
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="inlineStr"/>
@@ -3971,7 +3987,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 159х4,5–133х4,0</t>
+          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -3987,38 +4003,50 @@
         </is>
       </c>
       <c r="G122" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H122" s="3" t="n"/>
       <c r="I122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr"/>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>5. Внутренний противопожарный водопровод — В2</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="n"/>
-      <c r="D123" s="3" t="n"/>
-      <c r="E123" s="3" t="n"/>
-      <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
+      <c r="A123" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Переход стальной концентрический 133х4,0–89х3,5</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17378-2001</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr"/>
+      <c r="E123" s="3" t="inlineStr"/>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
+      <c r="I123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Шкаф пожарный навесной закрытый для двух пожарных кранов Ду65 и двух огнетушителей, с окном и местом для кнопки дистанционного пуска</t>
+          <t>Переход стальной концентрический 159х4,5–133х4,0</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>ШПК-320-21НЗК</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr"/>
@@ -4029,45 +4057,25 @@
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H124" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>огнетушители — по разделу ПБ</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Клапан пожарный запорный угловой 125° латунный Ду65 с головкой соединительной ГМ-65</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>КПЛМ 65-1, ГОСТ Р 53278-2009</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr"/>
-      <c r="E125" s="3" t="inlineStr"/>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H125" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I125" s="3" t="inlineStr"/>
+      <c r="A125" s="3" t="inlineStr"/>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>5. Внутренний противопожарный водопровод — В2</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n"/>
+      <c r="D125" s="3" t="n"/>
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -4075,12 +4083,12 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Рукав пожарный напорный Ду65, L=20 м, рабочее давление 1,6 МПа, с головками ГР-65</t>
+          <t>Шкаф пожарный навесной закрытый для двух пожарных кранов Ду65 и двух огнетушителей, с окном и местом для кнопки дистанционного пуска</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Ду65 L=20 м, ГОСТ Р 51049-2019</t>
+          <t>ШПК-320-21НЗК</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr"/>
@@ -4091,12 +4099,16 @@
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I126" s="3" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>огнетушители — по разделу ПБ</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -4104,12 +4116,12 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Ствол пожарный ручной с насадком Ø19 мм, головка ГР-70/65</t>
+          <t>Клапан пожарный запорный угловой 125° латунный Ду65 с головкой соединительной ГМ-65</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>РС-70 (насадок 19 мм), ГОСТ Р 53331-2009</t>
+          <t>КПЛМ 65-1, ГОСТ Р 53278-2009</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr"/>
@@ -4123,7 +4135,7 @@
         <v>60</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="I127" s="3" t="inlineStr"/>
     </row>
@@ -4133,12 +4145,12 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный межфланцевый Ду100 PN16 с рукояткой (секционирование кольца ВПВ)</t>
+          <t>Диафрагма стальная Ду65 с отверстием d=31 мм между клапаном ПК и соединительной головкой</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду65, d=31 мм</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr"/>
@@ -4149,14 +4161,14 @@
         </is>
       </c>
       <c r="G128" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>опломбировать в открытом положении</t>
+          <t>ПК подвал</t>
         </is>
       </c>
     </row>
@@ -4166,32 +4178,32 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Устройство дистанционного пуска «Пуск насосов» (в шкафу ПК)</t>
+          <t>Диафрагма стальная Ду65 с отверстием d=36 мм между клапаном ПК и соединительной головкой</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>ЭДУ 513-3АМ исп. 02 (зелёный)</t>
+          <t>Ду65, d=36 мм</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид» или аналог</t>
-        </is>
-      </c>
+      <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I129" s="3" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>ПК 1 этаж</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
@@ -4199,12 +4211,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Извещатель охранный магнитоконтактный (положение дверцы шкафа ПК)</t>
+          <t>Рукав пожарный напорный Ду65, L=20 м, рабочее давление 1,6 МПа, с головками ГР-65</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>ИО 102-20 Б2П</t>
+          <t>Ду65 L=20 м, ГОСТ Р 51049-2019</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr"/>
@@ -4215,153 +4227,151 @@
         </is>
       </c>
       <c r="G130" s="3" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>0.05</v>
+        <v>9</v>
       </c>
       <c r="I130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr"/>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>6. Трубопроводы и фасонные части системы В2</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n"/>
-      <c r="D131" s="3" t="n"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
+      <c r="A131" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Ствол пожарный ручной с насадком Ø19 мм, головка ГР-70/65</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>РС-70 (насадок 19 мм), ГОСТ Р 53331-2009</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr"/>
+      <c r="E131" s="3" t="inlineStr"/>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 76х3,5</t>
+          <t>Затвор дисковый поворотный межфланцевый Ду100 PN16 с рукояткой (секционирование кольца ВПВ)</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr"/>
       <c r="E132" s="3" t="inlineStr"/>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G132" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>6.26</v>
+        <v>6.5</v>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>с запасом 5 %</t>
+          <t>опломбировать в открытом положении</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89х3,5</t>
+          <t>Устройство дистанционного пуска «Пуск насосов» (в шкафу ПК)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>ЭДУ 513-3АМ исп. 02 (зелёный)</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr"/>
-      <c r="E133" s="3" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид» или аналог</t>
+        </is>
+      </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108х4,0</t>
+          <t>Извещатель охранный магнитоконтактный (положение дверцы шкафа ПК)</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>ИО 102-20 Б2П</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
       <c r="E134" s="3" t="inlineStr"/>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G134" s="3" t="n">
-        <v>226</v>
+        <v>30</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Тройник стальной приварной 108х4,0 с ответвлением 76х3,5 (врезка)</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>, ГОСТ 17376-2001</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr"/>
-      <c r="E135" s="3" t="inlineStr"/>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="n">
-        <v>22</v>
-      </c>
+      <c r="A135" s="3" t="inlineStr"/>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>6. Трубопроводы и фасонные части системы В2</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n"/>
+      <c r="D135" s="3" t="n"/>
+      <c r="E135" s="3" t="n"/>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="3" t="n"/>
       <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
@@ -4369,26 +4379,32 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108х4,0 с ответвлением 89х3,5 (врезка)</t>
+          <t>Труба стальная электросварная прямошовная 76х3,5</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr"/>
       <c r="E136" s="3" t="inlineStr"/>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G136" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H136" s="3" t="n"/>
-      <c r="I136" s="3" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -4396,26 +4412,32 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108х4,0</t>
+          <t>Труба стальная электросварная прямошовная 89х3,5</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H137" s="3" t="n"/>
-      <c r="I137" s="3" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -4423,26 +4445,32 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
+          <t>Труба стальная электросварная прямошовная 108х4,0</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr"/>
       <c r="E138" s="3" t="inlineStr"/>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G138" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -4450,12 +4478,12 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr"/>
@@ -4466,7 +4494,7 @@
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="inlineStr"/>
@@ -4477,12 +4505,12 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 89х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr"/>
@@ -4493,149 +4521,133 @@
         </is>
       </c>
       <c r="G140" s="3" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr"/>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>7. Узлы креплений трубопроводов (количество узлов в сборе)</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="n"/>
-      <c r="D141" s="3" t="n"/>
-      <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
+      <c r="A141" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Тройник стальной приварной 108х4,0</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17376-2001</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr"/>
+      <c r="E141" s="3" t="inlineStr"/>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
+      <c r="I141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду25 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 1</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G142" s="3" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="H142" s="3" t="n"/>
-      <c r="I142" s="3" t="inlineStr">
-        <is>
-          <t>количество узлов в сборе</t>
-        </is>
-      </c>
+      <c r="I142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду32 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 1</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="H143" s="3" t="n"/>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>количество узлов в сборе</t>
-        </is>
-      </c>
+      <c r="I143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду40 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 1</t>
+          <t>, ГОСТ 17378-2001</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr"/>
       <c r="E144" s="3" t="inlineStr"/>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G144" s="3" t="n">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="H144" s="3" t="n"/>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>количество узлов в сборе</t>
-        </is>
-      </c>
+      <c r="I144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>Узел крепления трубы Ду50 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>узел 4, тип 1</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr"/>
-      <c r="E145" s="3" t="inlineStr"/>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>123</v>
-      </c>
+      <c r="A145" s="3" t="inlineStr"/>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>7. Узлы креплений трубопроводов (количество узлов в сборе)</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n"/>
+      <c r="D145" s="3" t="n"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="3" t="n"/>
       <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>количество узлов в сборе</t>
-        </is>
-      </c>
+      <c r="I145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -4643,7 +4655,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду65 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду25 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -4659,7 +4671,7 @@
         </is>
       </c>
       <c r="G146" s="3" t="n">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="H146" s="3" t="n"/>
       <c r="I146" s="3" t="inlineStr">
@@ -4674,7 +4686,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду32 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -4690,7 +4702,7 @@
         </is>
       </c>
       <c r="G147" s="3" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="inlineStr">
@@ -4705,7 +4717,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду100 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду40 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -4721,7 +4733,7 @@
         </is>
       </c>
       <c r="G148" s="3" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="inlineStr">
@@ -4736,7 +4748,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду125 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду50 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -4752,7 +4764,7 @@
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="inlineStr">
@@ -4767,7 +4779,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду150 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду65 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -4783,7 +4795,7 @@
         </is>
       </c>
       <c r="G150" s="3" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="inlineStr">
@@ -4798,7 +4810,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду65 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду80 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -4814,7 +4826,7 @@
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" s="3" t="n"/>
       <c r="I151" s="3" t="inlineStr">
@@ -4829,7 +4841,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду100 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -4845,7 +4857,7 @@
         </is>
       </c>
       <c r="G152" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="inlineStr">
@@ -4860,7 +4872,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду100 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду125 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -4876,7 +4888,7 @@
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="inlineStr">
@@ -4891,12 +4903,12 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду25 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду150 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 2</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr"/>
@@ -4907,7 +4919,7 @@
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>145</v>
+        <v>31</v>
       </c>
       <c r="H154" s="3" t="n"/>
       <c r="I154" s="3" t="inlineStr">
@@ -4922,12 +4934,12 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду32 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду65 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 2</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr"/>
@@ -4938,7 +4950,7 @@
         </is>
       </c>
       <c r="G155" s="3" t="n">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="inlineStr">
@@ -4953,12 +4965,12 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду40 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду80 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 2</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr"/>
@@ -4969,7 +4981,7 @@
         </is>
       </c>
       <c r="G156" s="3" t="n">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="inlineStr">
@@ -4984,12 +4996,12 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду50 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду100 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 2</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr"/>
@@ -5000,7 +5012,7 @@
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="inlineStr">
@@ -5015,7 +5027,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду25 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -5031,7 +5043,7 @@
         </is>
       </c>
       <c r="G158" s="3" t="n">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="inlineStr">
@@ -5046,7 +5058,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду125 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду32 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -5062,7 +5074,7 @@
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="inlineStr">
@@ -5077,7 +5089,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду150 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду40 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -5093,7 +5105,7 @@
         </is>
       </c>
       <c r="G160" s="3" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="H160" s="3" t="n"/>
       <c r="I160" s="3" t="inlineStr">
@@ -5108,12 +5120,12 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+          <t>Узел крепления трубы Ду50 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 3</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr"/>
@@ -5124,7 +5136,7 @@
         </is>
       </c>
       <c r="G161" s="3" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H161" s="3" t="n"/>
       <c r="I161" s="3" t="inlineStr">
@@ -5139,12 +5151,12 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду100 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+          <t>Узел крепления трубы Ду80 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 3</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr"/>
@@ -5155,7 +5167,7 @@
         </is>
       </c>
       <c r="G162" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="inlineStr">
@@ -5170,12 +5182,12 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду150 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+          <t>Узел крепления трубы Ду125 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 3</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr"/>
@@ -5186,7 +5198,7 @@
         </is>
       </c>
       <c r="G163" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="inlineStr">
@@ -5196,127 +5208,143 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr"/>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>7а. Изделия и материалы (системы В2, В21, В22)</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="n"/>
-      <c r="D164" s="3" t="n"/>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="n"/>
+      <c r="A164" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Узел крепления трубы Ду150 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>узел 4, тип 2</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr"/>
+      <c r="E164" s="3" t="inlineStr"/>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>34</v>
+      </c>
       <c r="H164" s="3" t="n"/>
-      <c r="I164" s="3" t="n"/>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду25</t>
+          <t>Узел крепления трубы Ду80 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>узел 4, тип 3</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr"/>
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="H165" s="3" t="n"/>
-      <c r="I165" s="3" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду32</t>
+          <t>Узел крепления трубы Ду100 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>узел 4, тип 3</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr"/>
       <c r="E166" s="3" t="inlineStr"/>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G166" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H166" s="3" t="n"/>
-      <c r="I166" s="3" t="inlineStr"/>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду40</t>
+          <t>Узел крепления трубы Ду150 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 2</t>
+          <t>узел 4, тип 3</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr"/>
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H167" s="3" t="n"/>
-      <c r="I167" s="3" t="inlineStr"/>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду50</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>, см. узел 2</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr"/>
-      <c r="E168" s="3" t="inlineStr"/>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="n">
-        <v>63</v>
-      </c>
+      <c r="A168" s="3" t="inlineStr"/>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>7а. Изделия и материалы (системы В2, В21, В22)</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n"/>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="3" t="n"/>
       <c r="H168" s="3" t="n"/>
-      <c r="I168" s="3" t="inlineStr"/>
+      <c r="I168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -5324,7 +5352,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду80</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду25</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -5340,7 +5368,7 @@
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="inlineStr"/>
@@ -5351,7 +5379,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду100</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду32</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -5367,7 +5395,7 @@
         </is>
       </c>
       <c r="G170" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="inlineStr"/>
@@ -5378,7 +5406,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду125</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду40</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -5394,7 +5422,7 @@
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="inlineStr"/>
@@ -5405,7 +5433,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду150</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду50</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -5421,7 +5449,7 @@
         </is>
       </c>
       <c r="G172" s="3" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="H172" s="3" t="n"/>
       <c r="I172" s="3" t="inlineStr"/>
@@ -5432,12 +5460,12 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду80</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду80</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 3</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr"/>
@@ -5448,7 +5476,7 @@
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H173" s="3" t="n"/>
       <c r="I173" s="3" t="inlineStr"/>
@@ -5459,12 +5487,12 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду100</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду100</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 3</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr"/>
@@ -5475,7 +5503,7 @@
         </is>
       </c>
       <c r="G174" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H174" s="3" t="n"/>
       <c r="I174" s="3" t="inlineStr"/>
@@ -5486,12 +5514,12 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду150</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду125</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 3</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr"/>
@@ -5513,26 +5541,26 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Состав огнезащитный терморасширяющийся (герметик) для заделки зазоров в гильзах, EI не ниже предела огнестойкости преграды</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr"/>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду150</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 2</t>
+        </is>
+      </c>
       <c r="D176" s="3" t="inlineStr"/>
       <c r="E176" s="3" t="inlineStr"/>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G176" s="3" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="H176" s="3" t="n"/>
-      <c r="I176" s="3" t="inlineStr">
-        <is>
-          <t>0,25 кг на проход</t>
-        </is>
-      </c>
+      <c r="I176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -5540,30 +5568,26 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Грунтовка ГФ-021 (1 слой)</t>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду80</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 25129-2020</t>
+          <t>, см. узел 3</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr"/>
       <c r="E177" s="3" t="inlineStr"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="H177" s="3" t="n"/>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>S=692 м²</t>
-        </is>
-      </c>
+      <c r="I177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
@@ -5571,177 +5595,153 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 красная (2 слоя)</t>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду100</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 6465-76</t>
+          <t>, см. узел 3</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr"/>
       <c r="E178" s="3" t="inlineStr"/>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G178" s="3" t="n">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="H178" s="3" t="n"/>
       <c r="I178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr"/>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>8. Автоматическая установка порошкового пожаротушения помещения ВРУ (пом. 06)</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="n"/>
-      <c r="D179" s="3" t="n"/>
-      <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="n"/>
-      <c r="G179" s="3" t="n"/>
+      <c r="A179" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду150</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 3</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr"/>
+      <c r="E179" s="3" t="inlineStr"/>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="H179" s="3" t="n"/>
-      <c r="I179" s="3" t="n"/>
+      <c r="I179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Модуль порошкового пожаротушения закачного типа, масса ОТВ 8 кг, защищаемый объём (класс В) не менее 32 м³, электропуск</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>МПП(Н)-8 (типа «Буран-8» или аналог), ГОСТ Р 53286-2009</t>
-        </is>
-      </c>
+          <t>Состав огнезащитный терморасширяющийся (герметик) для заделки зазоров в гильзах, EI не ниже предела огнестойкости преграды</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr"/>
       <c r="D180" s="3" t="inlineStr"/>
       <c r="E180" s="3" t="inlineStr"/>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G180" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H180" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I180" s="3" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="inlineStr">
+        <is>
+          <t>0,25 кг на проход</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Запас модулей порошкового пожаротушения (100 %)</t>
+          <t>Грунтовка ГФ-021 (1 слой)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>то же</t>
+          <t>, ГОСТ 25129-2020</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr"/>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H181" s="3" t="n">
-        <v>13</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="H181" s="3" t="n"/>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>хранение на объекте</t>
+          <t>S=692 м²</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Блок управления пожаротушением на одно направление</t>
+          <t>Эмаль ПФ-115 красная (2 слоя)</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>С2000-АСПТ</t>
+          <t>, ГОСТ 6465-76</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr"/>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E182" s="3" t="inlineStr"/>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G182" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H182" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>у входа в пом. 06</t>
-        </is>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>Извещатель пожарный дымовой оптико-электронный адресно-аналоговый</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>ДИП-34А-04</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr"/>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H183" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I183" s="3" t="inlineStr">
-        <is>
-          <t>пуск по 2 из 3</t>
-        </is>
-      </c>
+      <c r="A183" s="3" t="inlineStr"/>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>8. Автоматическая установка порошкового пожаротушения помещения ВРУ (пом. 06)</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n">
@@ -5749,36 +5749,28 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Устройство дистанционного пуска «Пуск порошка» (жёлтое, с защитной крышкой)</t>
+          <t>Модуль порошкового пожаротушения закачного типа, масса ОТВ 8 кг, защищаемый объём (класс В) не менее 32 м³, электропуск</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>ЭДУ 513-3АМ исп. 01</t>
+          <t>МПП(Н)-8 (типа «Буран-8» или аналог), ГОСТ Р 53286-2009</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr"/>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E184" s="3" t="inlineStr"/>
       <c r="F184" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G184" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I184" s="3" t="inlineStr">
-        <is>
-          <t>у входа</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
@@ -5786,12 +5778,12 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «ПОРОШОК! УХОДИ!» 24 В</t>
+          <t>Запас модулей порошкового пожаротушения (100 %)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Молния-24</t>
+          <t>то же</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr"/>
@@ -5802,14 +5794,14 @@
         </is>
       </c>
       <c r="G185" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>0.25</v>
+        <v>13</v>
       </c>
       <c r="I185" s="3" t="inlineStr">
         <is>
-          <t>внутри</t>
+          <t>хранение на объекте</t>
         </is>
       </c>
     </row>
@@ -5819,16 +5811,20 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «ПОРОШОК! НЕ ВХОДИ!» 24 В</t>
+          <t>Блок управления пожаротушением на одно направление</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Молния-24</t>
+          <t>С2000-АСПТ</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr"/>
-      <c r="E186" s="3" t="inlineStr"/>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -5838,11 +5834,11 @@
         <v>1</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>0.25</v>
+        <v>1.1</v>
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>над дверью снаружи</t>
+          <t>у входа в пом. 06</t>
         </is>
       </c>
     </row>
@@ -5852,30 +5848,34 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «АВТОМАТИКА ОТКЛЮЧЕНА» 24 В</t>
+          <t>Извещатель пожарный дымовой оптико-электронный адресно-аналоговый</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Молния-24</t>
+          <t>ДИП-34А-04</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr"/>
-      <c r="E187" s="3" t="inlineStr"/>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G187" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>снаружи</t>
+          <t>пуск по 2 из 3</t>
         </is>
       </c>
     </row>
@@ -5885,16 +5885,20 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Оповещатель звуковой 24 В, 105 дБ</t>
+          <t>Устройство дистанционного пуска «Пуск порошка» (жёлтое, с защитной крышкой)</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Маяк-24-3М</t>
+          <t>ЭДУ 513-3АМ исп. 01</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr"/>
-      <c r="E188" s="3" t="inlineStr"/>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -5904,11 +5908,11 @@
         <v>1</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>внутри</t>
+          <t>у входа</t>
         </is>
       </c>
     </row>
@@ -5918,12 +5922,12 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Извещатель магнитоконтактный (контроль закрытия двери)</t>
+          <t>Табло световое «ПОРОШОК! УХОДИ!» 24 В</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>ИО 102-26 «Аякс»</t>
+          <t>Молния-24</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr"/>
@@ -5937,9 +5941,13 @@
         <v>1</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I189" s="3" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>внутри</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n">
@@ -5947,32 +5955,32 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
+          <t>Табло световое «ПОРОШОК! НЕ ВХОДИ!» 24 В</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>РИП-24 исп. 01</t>
+          <t>Молния-24</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr"/>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E190" s="3" t="inlineStr"/>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G190" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H190" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I190" s="3" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
+        <is>
+          <t>над дверью снаружи</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n">
@@ -5980,12 +5988,12 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Коробка коммутационная огнестойкая (Е90)</t>
+          <t>Табло световое «АВТОМАТИКА ОТКЛЮЧЕНА» 24 В</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>КМ-О (4к)-IP41</t>
+          <t>Молния-24</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr"/>
@@ -5996,48 +6004,66 @@
         </is>
       </c>
       <c r="G191" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I191" s="3" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="I191" s="3" t="inlineStr">
+        <is>
+          <t>снаружи</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr"/>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>9. Автоматизация систем водяного пожаротушения</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="n"/>
-      <c r="D192" s="3" t="n"/>
-      <c r="E192" s="3" t="n"/>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
-      <c r="H192" s="3" t="n"/>
-      <c r="I192" s="3" t="n"/>
+      <c r="A192" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Оповещатель звуковой 24 В, 105 дБ</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Маяк-24-3М</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr"/>
+      <c r="E192" s="3" t="inlineStr"/>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I192" s="3" t="inlineStr">
+        <is>
+          <t>внутри</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Прибор управления насосной станцией пожаротушения (основной, резервный, жокей-насос)</t>
+          <t>Извещатель магнитоконтактный (контроль закрытия двери)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Поток-3Н</t>
+          <t>ИО 102-26 «Аякс»</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr"/>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -6047,26 +6073,22 @@
         <v>1</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I193" s="3" t="inlineStr">
-        <is>
-          <t>насосная</t>
-        </is>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Шкаф контрольно-пусковой для электродвигателя до 30 кВт, 380 В</t>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>ШКП-30</t>
+          <t>РИП-24 исп. 01</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr"/>
@@ -6077,94 +6099,60 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G194" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="I194" s="3" t="inlineStr">
-        <is>
-          <t>Н1, Н2</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Шкаф контрольно-пусковой для электродвигателя до 4 кВт, 380 В</t>
+          <t>Коробка коммутационная огнестойкая (Е90)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>ШКП-4</t>
+          <t>КМ-О (4к)-IP41</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr"/>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G195" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I195" s="3" t="inlineStr">
-        <is>
-          <t>Н3</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="I195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n">
-        <v>182</v>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>Контроллер двухпроводной линии связи (адресные устройства ПТ)</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="inlineStr">
-        <is>
-          <t>С2000-КДЛ-2И</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="inlineStr"/>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I196" s="3" t="inlineStr">
-        <is>
-          <t>RS-485 к ППКУП «Сириус» (пом. 03)</t>
-        </is>
-      </c>
+      <c r="A196" s="3" t="inlineStr"/>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>9. Автоматизация систем водяного пожаротушения</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
+      <c r="F196" s="3" t="n"/>
+      <c r="G196" s="3" t="n"/>
+      <c r="H196" s="3" t="n"/>
+      <c r="I196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n">
@@ -6172,12 +6160,12 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Адресный расширитель на 2 входа (контроль затворов, дверей шкафов ПК, кнопок «Пуск насосов», аварийного уровня в приямке)</t>
+          <t>Прибор управления насосной станцией пожаротушения (основной, резервный, жокей-насос)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>С2000-АР2 исп. 02</t>
+          <t>Поток-3Н</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr"/>
@@ -6192,12 +6180,16 @@
         </is>
       </c>
       <c r="G197" s="3" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I197" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t>насосная</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
@@ -6205,12 +6197,12 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
+          <t>Шкаф контрольно-пусковой для электродвигателя до 30 кВт, 380 В</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>РИП-24 исп. 01</t>
+          <t>ШКП-30</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr"/>
@@ -6221,16 +6213,20 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G198" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I198" s="3" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>Н1, Н2</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n">
@@ -6238,12 +6234,20 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Шкаф монтажный навесной 600х600х250 IP54 для приборов автоматики ПТ</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr"/>
+          <t>Шкаф контрольно-пусковой для электродвигателя до 4 кВт, 380 В</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>ШКП-4</t>
+        </is>
+      </c>
       <c r="D199" s="3" t="inlineStr"/>
-      <c r="E199" s="3" t="inlineStr"/>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -6253,152 +6257,160 @@
         <v>1</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>насосная</t>
+          <t>Н3</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="inlineStr"/>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>10. Кабельные изделия (см. кабельный журнал ПТ.КЖ)</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="n"/>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n"/>
+      <c r="A200" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>Контроллер двухпроводной линии связи (адресные устройства ПТ)</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>С2000-КДЛ-2И</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr"/>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>RS-485 к ППКУП «Сириус» (пом. 03)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 5х6</t>
+          <t>Адресный расширитель на 2 входа (контроль затворов, дверей шкафов ПК, кнопок «Пуск насосов», аварийного уровня в приямке)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>С2000-АР2 исп. 02</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr"/>
-      <c r="E201" s="3" t="inlineStr"/>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G201" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="H201" s="3" t="n"/>
-      <c r="I201" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I201" s="3" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 5х2,5</t>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>РИП-24 исп. 01</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr"/>
-      <c r="E202" s="3" t="inlineStr"/>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G202" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="H202" s="3" t="n"/>
-      <c r="I202" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 3х1,5</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
-        </is>
-      </c>
+          <t>Шкаф монтажный навесной 600х600х250 IP54 для приборов автоматики ПТ</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr"/>
       <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr"/>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G203" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="H203" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>с запасом 10 %</t>
+          <t>насосная</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>Кабель ВВГнг(А)-FRLS 4х6</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="inlineStr"/>
-      <c r="E204" s="3" t="inlineStr"/>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="A204" s="3" t="inlineStr"/>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>10. Кабельные изделия (см. кабельный журнал ПТ.КЖ)</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n"/>
+      <c r="D204" s="3" t="n"/>
+      <c r="E204" s="3" t="n"/>
+      <c r="F204" s="3" t="n"/>
+      <c r="G204" s="3" t="n"/>
       <c r="H204" s="3" t="n"/>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n">
@@ -6406,7 +6418,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 4х1,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 5х6</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -6422,7 +6434,7 @@
         </is>
       </c>
       <c r="G205" s="3" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="H205" s="3" t="n"/>
       <c r="I205" s="3" t="inlineStr">
@@ -6437,12 +6449,12 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 2х2х0,75</t>
+          <t>Кабель ВВГнг(А)-FRLS 5х2,5</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr"/>
@@ -6453,7 +6465,7 @@
         </is>
       </c>
       <c r="G206" s="3" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H206" s="3" t="n"/>
       <c r="I206" s="3" t="inlineStr">
@@ -6468,12 +6480,12 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1х2х1,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 3х1,5</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr"/>
@@ -6484,7 +6496,7 @@
         </is>
       </c>
       <c r="G207" s="3" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H207" s="3" t="n"/>
       <c r="I207" s="3" t="inlineStr">
@@ -6499,12 +6511,12 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1х2х0,75</t>
+          <t>Кабель ВВГнг(А)-FRLS 4х6</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr"/>
@@ -6515,7 +6527,7 @@
         </is>
       </c>
       <c r="G208" s="3" t="n">
-        <v>832</v>
+        <v>11</v>
       </c>
       <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="inlineStr">
@@ -6530,12 +6542,12 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСЭнг(А)-FRLS 1х2х0,75</t>
+          <t>Кабель ВВГнг(А)-FRLS 4х1,5</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>КПСЭнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr"/>
@@ -6546,7 +6558,7 @@
         </is>
       </c>
       <c r="G209" s="3" t="n">
-        <v>270</v>
+        <v>18</v>
       </c>
       <c r="H209" s="3" t="n"/>
       <c r="I209" s="3" t="inlineStr">
@@ -6561,10 +6573,14 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Труба гофрированная ПВХ безгалогенная Ø20 мм с протяжкой</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr"/>
+          <t>Кабель КПСнг(А)-FRLS 2х2х0,75</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
       <c r="D210" s="3" t="inlineStr"/>
       <c r="E210" s="3" t="inlineStr"/>
       <c r="F210" s="3" t="inlineStr">
@@ -6573,12 +6589,12 @@
         </is>
       </c>
       <c r="G210" s="3" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="H210" s="3" t="n"/>
       <c r="I210" s="3" t="inlineStr">
         <is>
-          <t>опуски к приборам</t>
+          <t>с запасом 10 %</t>
         </is>
       </c>
     </row>
@@ -6588,10 +6604,14 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Металлорукав в ПВХ изоляции Ø25 мм</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr"/>
+          <t>Кабель КПСнг(А)-FRLS 1х2х1,5</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
       <c r="D211" s="3" t="inlineStr"/>
       <c r="E211" s="3" t="inlineStr"/>
       <c r="F211" s="3" t="inlineStr">
@@ -6600,12 +6620,12 @@
         </is>
       </c>
       <c r="G211" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H211" s="3" t="n"/>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>подключение электродвигателей</t>
+          <t>с запасом 10 %</t>
         </is>
       </c>
     </row>
@@ -6615,10 +6635,14 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Лоток кабельный перфорированный 100х50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="inlineStr"/>
+          <t>Кабель КПСнг(А)-FRLS 1х2х0,75</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
       <c r="D212" s="3" t="inlineStr"/>
       <c r="E212" s="3" t="inlineStr"/>
       <c r="F212" s="3" t="inlineStr">
@@ -6627,10 +6651,122 @@
         </is>
       </c>
       <c r="G212" s="3" t="n">
-        <v>70</v>
+        <v>832</v>
       </c>
       <c r="H212" s="3" t="n"/>
       <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Кабель КПСЭнг(А)-FRLS 1х2х0,75</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>КПСЭнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr"/>
+      <c r="E213" s="3" t="inlineStr"/>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="H213" s="3" t="n"/>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>Труба гофрированная ПВХ безгалогенная Ø20 мм с протяжкой</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr"/>
+      <c r="D214" s="3" t="inlineStr"/>
+      <c r="E214" s="3" t="inlineStr"/>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H214" s="3" t="n"/>
+      <c r="I214" s="3" t="inlineStr">
+        <is>
+          <t>опуски к приборам</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Металлорукав в ПВХ изоляции Ø25 мм</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr"/>
+      <c r="D215" s="3" t="inlineStr"/>
+      <c r="E215" s="3" t="inlineStr"/>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H215" s="3" t="n"/>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>подключение электродвигателей</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Лоток кабельный перфорированный 100х50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr"/>
+      <c r="D216" s="3" t="inlineStr"/>
+      <c r="E216" s="3" t="inlineStr"/>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H216" s="3" t="n"/>
+      <c r="I216" s="3" t="inlineStr">
         <is>
           <t>пом. 06 – тамбур 92 – пом. 05 – насосная</t>
         </is>

--- a/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
+++ b/pt-dok-pavilion-23/out/ОПР-01_24_2024-ДП1-ПТ.С_спецификация.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I216"/>
+  <dimension ref="A1:I217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4099,14 +4099,14 @@
         </is>
       </c>
       <c r="G126" s="3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>38</v>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>огнетушители — по разделу ПБ</t>
+          <t>1 и 2 этажи; огнетушители — по разделу ПБ</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Клапан пожарный запорный угловой 125° латунный Ду65 с головкой соединительной ГМ-65</t>
+          <t>Шкаф пожарный навесной закрытый для одного пожарного крана Ду65, с окном</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>КПЛМ 65-1, ГОСТ Р 53278-2009</t>
+          <t>ШПК-310НЗК (540х650х230)</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr"/>
@@ -4132,12 +4132,16 @@
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I127" s="3" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>подвал, по два на точку</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
@@ -4145,12 +4149,12 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Диафрагма стальная Ду65 с отверстием d=31 мм между клапаном ПК и соединительной головкой</t>
+          <t>Клапан пожарный запорный угловой 125° латунный Ду65 с головкой соединительной ГМ-65</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Ду65, d=31 мм</t>
+          <t>КПЛМ 65-1, ГОСТ Р 53278-2009</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr"/>
@@ -4161,16 +4165,12 @@
         </is>
       </c>
       <c r="G128" s="3" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>ПК подвал</t>
-        </is>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="I128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Диафрагма стальная Ду65 с отверстием d=36 мм между клапаном ПК и соединительной головкой</t>
+          <t>Диафрагма стальная Ду65 с отверстием d=32 мм между клапаном ПК и соединительной головкой</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Ду65, d=36 мм</t>
+          <t>Ду65, d=32 мм</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr"/>
@@ -4194,14 +4194,14 @@
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H129" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>ПК 1 этаж</t>
+          <t>ПК подвал</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Рукав пожарный напорный Ду65, L=20 м, рабочее давление 1,6 МПа, с головками ГР-65</t>
+          <t>Диафрагма стальная Ду65 с отверстием d=36 мм между клапаном ПК и соединительной головкой</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Ду65 L=20 м, ГОСТ Р 51049-2019</t>
+          <t>Ду65, d=36 мм</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr"/>
@@ -4227,12 +4227,16 @@
         </is>
       </c>
       <c r="G130" s="3" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I130" s="3" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>ПК 1 этаж</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
@@ -4240,12 +4244,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Ствол пожарный ручной с насадком Ø19 мм, головка ГР-70/65</t>
+          <t>Рукав пожарный напорный Ду65, L=20 м, рабочее давление 1,6 МПа, с головками ГР-65</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>РС-70 (насадок 19 мм), ГОСТ Р 53331-2009</t>
+          <t>Ду65 L=20 м, ГОСТ Р 51049-2019</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr"/>
@@ -4259,7 +4263,7 @@
         <v>60</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="I131" s="3" t="inlineStr"/>
     </row>
@@ -4269,12 +4273,12 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Затвор дисковый поворотный межфланцевый Ду100 PN16 с рукояткой (секционирование кольца ВПВ)</t>
+          <t>Ствол пожарный ручной с насадком Ø19 мм, головка ГР-70/65</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>РС-70 (насадок 19 мм), ГОСТ Р 53331-2009</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr"/>
@@ -4285,16 +4289,12 @@
         </is>
       </c>
       <c r="G132" s="3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I132" s="3" t="inlineStr">
-        <is>
-          <t>опломбировать в открытом положении</t>
-        </is>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="I132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -4302,32 +4302,32 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Устройство дистанционного пуска «Пуск насосов» (в шкафу ПК)</t>
+          <t>Затвор дисковый поворотный межфланцевый Ду100 PN16 с рукояткой (секционирование кольца ВПВ)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>ЭДУ 513-3АМ исп. 02 (зелёный)</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr"/>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид» или аналог</t>
-        </is>
-      </c>
+      <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I133" s="3" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>опломбировать в открытом положении</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
@@ -4335,16 +4335,20 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Извещатель охранный магнитоконтактный (положение дверцы шкафа ПК)</t>
+          <t>Устройство дистанционного пуска «Пуск насосов» (в шкафу ПК)</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>ИО 102-20 Б2П</t>
+          <t>ЭДУ 513-3АМ исп. 02 (зелёный)</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
-      <c r="E134" s="3" t="inlineStr"/>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид» или аналог</t>
+        </is>
+      </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -4354,57 +4358,57 @@
         <v>30</v>
       </c>
       <c r="H134" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>в подвале — в одном из двух шкафов</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Извещатель охранный магнитоконтактный (положение дверцы шкафа ПК)</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>ИО 102-20 Б2П</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H135" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="I134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr"/>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr"/>
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>6. Трубопроводы и фасонные части системы В2</t>
         </is>
       </c>
-      <c r="C135" s="3" t="n"/>
-      <c r="D135" s="3" t="n"/>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>Труба стальная электросварная прямошовная 76х3,5</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr"/>
-      <c r="E136" s="3" t="inlineStr"/>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H136" s="3" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 5 %</t>
-        </is>
-      </c>
+      <c r="C136" s="3" t="n"/>
+      <c r="D136" s="3" t="n"/>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -4412,12 +4416,12 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 89х3,5</t>
+          <t>Труба стальная электросварная прямошовная 76х3,5</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>76х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr"/>
@@ -4428,10 +4432,10 @@
         </is>
       </c>
       <c r="G137" s="3" t="n">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>7.38</v>
+        <v>6.26</v>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
@@ -4445,12 +4449,12 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Труба стальная электросварная прямошовная 108х4,0</t>
+          <t>Труба стальная электросварная прямошовная 89х3,5</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
+          <t>89х3,5, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr"/>
@@ -4461,10 +4465,10 @@
         </is>
       </c>
       <c r="G138" s="3" t="n">
-        <v>226</v>
+        <v>150</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>10.26</v>
+        <v>7.38</v>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
@@ -4478,26 +4482,32 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108х4,0 с ответвлением 76х3,5 (врезка)</t>
+          <t>Труба стальная электросварная прямошовная 108х4,0</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17376-2001</t>
+          <t>108х4,0, ГОСТ 10704-91 / В-Ст3сп ГОСТ 10705-80</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>с запасом 5 %</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -4505,7 +4515,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108х4,0 с ответвлением 89х3,5 (врезка)</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 76х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -4521,7 +4531,7 @@
         </is>
       </c>
       <c r="G140" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="inlineStr"/>
@@ -4532,7 +4542,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Тройник стальной приварной 108х4,0</t>
+          <t>Тройник стальной приварной 108х4,0 с ответвлением 89х3,5 (врезка)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -4548,7 +4558,7 @@
         </is>
       </c>
       <c r="G141" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="inlineStr"/>
@@ -4559,12 +4569,12 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
+          <t>Тройник стальной приварной 108х4,0</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17375-2001</t>
+          <t>, ГОСТ 17376-2001</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr"/>
@@ -4575,7 +4585,7 @@
         </is>
       </c>
       <c r="G142" s="3" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="inlineStr"/>
@@ -4586,7 +4596,7 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
+          <t>Отвод стальной крутоизогнутый 90° 89х3,5</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -4602,7 +4612,7 @@
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="inlineStr"/>
@@ -4613,12 +4623,12 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
+          <t>Отвод стальной крутоизогнутый 90° 108х4,0</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 17378-2001</t>
+          <t>, ГОСТ 17375-2001</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr"/>
@@ -4629,56 +4639,52 @@
         </is>
       </c>
       <c r="G144" s="3" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr"/>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="A145" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Переход стальной концентрический 89х3,5–76х3,5</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 17378-2001</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr"/>
+      <c r="E145" s="3" t="inlineStr"/>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr"/>
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>7. Узлы креплений трубопроводов (количество узлов в сборе)</t>
         </is>
       </c>
-      <c r="C145" s="3" t="n"/>
-      <c r="D145" s="3" t="n"/>
-      <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="3" t="n"/>
-      <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>Узел крепления трубы Ду25 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>узел 4, тип 1</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr"/>
-      <c r="E146" s="3" t="inlineStr"/>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>133</v>
-      </c>
+      <c r="C146" s="3" t="n"/>
+      <c r="D146" s="3" t="n"/>
+      <c r="E146" s="3" t="n"/>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="3" t="n"/>
       <c r="H146" s="3" t="n"/>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>количество узлов в сборе</t>
-        </is>
-      </c>
+      <c r="I146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -4686,7 +4692,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду32 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду25 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -4702,7 +4708,7 @@
         </is>
       </c>
       <c r="G147" s="3" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="H147" s="3" t="n"/>
       <c r="I147" s="3" t="inlineStr">
@@ -4717,7 +4723,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду40 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду32 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -4733,7 +4739,7 @@
         </is>
       </c>
       <c r="G148" s="3" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="inlineStr">
@@ -4748,7 +4754,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду50 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду40 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -4764,7 +4770,7 @@
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="inlineStr">
@@ -4779,7 +4785,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду65 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду50 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -4795,7 +4801,7 @@
         </is>
       </c>
       <c r="G150" s="3" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="inlineStr">
@@ -4810,7 +4816,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду65 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -4826,7 +4832,7 @@
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H151" s="3" t="n"/>
       <c r="I151" s="3" t="inlineStr">
@@ -4841,7 +4847,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду100 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду80 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -4857,7 +4863,7 @@
         </is>
       </c>
       <c r="G152" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H152" s="3" t="n"/>
       <c r="I152" s="3" t="inlineStr">
@@ -4872,7 +4878,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду125 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду100 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -4888,7 +4894,7 @@
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="inlineStr">
@@ -4903,7 +4909,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду150 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду125 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -4919,7 +4925,7 @@
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="H154" s="3" t="n"/>
       <c r="I154" s="3" t="inlineStr">
@@ -4934,7 +4940,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду65 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду150 к монолитному перекрытию по профлисту (тип 1): анкер клиновой, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -4950,7 +4956,7 @@
         </is>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H155" s="3" t="n"/>
       <c r="I155" s="3" t="inlineStr">
@@ -4965,7 +4971,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду65 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -4981,7 +4987,7 @@
         </is>
       </c>
       <c r="G156" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H156" s="3" t="n"/>
       <c r="I156" s="3" t="inlineStr">
@@ -4996,7 +5002,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду100 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду80 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -5012,7 +5018,7 @@
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="inlineStr">
@@ -5027,12 +5033,12 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду25 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду100 к перекрытию над техническим подвалом (тип 1): анкер клиновой, шпилька, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 2</t>
+          <t>узел 4, тип 1</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr"/>
@@ -5043,7 +5049,7 @@
         </is>
       </c>
       <c r="G158" s="3" t="n">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="inlineStr">
@@ -5058,7 +5064,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду32 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду25 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -5074,7 +5080,7 @@
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="inlineStr">
@@ -5089,7 +5095,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду40 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду32 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -5105,7 +5111,7 @@
         </is>
       </c>
       <c r="G160" s="3" t="n">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H160" s="3" t="n"/>
       <c r="I160" s="3" t="inlineStr">
@@ -5120,7 +5126,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду50 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
+          <t>Узел крепления трубы Ду40 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -5136,7 +5142,7 @@
         </is>
       </c>
       <c r="G161" s="3" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="H161" s="3" t="n"/>
       <c r="I161" s="3" t="inlineStr">
@@ -5151,7 +5157,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду50 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М10</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -5167,7 +5173,7 @@
         </is>
       </c>
       <c r="G162" s="3" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="inlineStr">
@@ -5182,7 +5188,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду125 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду80 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -5198,7 +5204,7 @@
         </is>
       </c>
       <c r="G163" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H163" s="3" t="n"/>
       <c r="I163" s="3" t="inlineStr">
@@ -5213,7 +5219,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду150 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
+          <t>Узел крепления трубы Ду125 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -5229,7 +5235,7 @@
         </is>
       </c>
       <c r="G164" s="3" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H164" s="3" t="n"/>
       <c r="I164" s="3" t="inlineStr">
@@ -5244,12 +5250,12 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду80 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+          <t>Узел крепления трубы Ду150 к прогону или балке покрытия (тип 2): струбцина балочная, шпилька, гайка соединительная, хомут с вкладышем, шпилька М12</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>узел 4, тип 3</t>
+          <t>узел 4, тип 2</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr"/>
@@ -5260,7 +5266,7 @@
         </is>
       </c>
       <c r="G165" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="inlineStr">
@@ -5275,7 +5281,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду100 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+          <t>Узел крепления трубы Ду80 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -5291,7 +5297,7 @@
         </is>
       </c>
       <c r="G166" s="3" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H166" s="3" t="n"/>
       <c r="I166" s="3" t="inlineStr">
@@ -5306,7 +5312,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Узел крепления трубы Ду150 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+          <t>Узел крепления трубы Ду100 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -5322,7 +5328,7 @@
         </is>
       </c>
       <c r="G167" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H167" s="3" t="n"/>
       <c r="I167" s="3" t="inlineStr">
@@ -5332,46 +5338,50 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr"/>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="A168" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Узел крепления трубы Ду150 вертикального трубопровода к стене или колонне (тип 3): кронштейн, хомут с вкладышем, анкеры, шпилька М12</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>узел 4, тип 3</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr"/>
+      <c r="E168" s="3" t="inlineStr"/>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H168" s="3" t="n"/>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>количество узлов в сборе</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr"/>
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>7а. Изделия и материалы (системы В2, В21, В22)</t>
         </is>
       </c>
-      <c r="C168" s="3" t="n"/>
-      <c r="D168" s="3" t="n"/>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="3" t="n"/>
-      <c r="H168" s="3" t="n"/>
-      <c r="I168" s="3" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>157</v>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду25</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>, см. узел 2</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr"/>
-      <c r="E169" s="3" t="inlineStr"/>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="n">
-        <v>66</v>
-      </c>
+      <c r="C169" s="3" t="n"/>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
       <c r="H169" s="3" t="n"/>
-      <c r="I169" s="3" t="inlineStr"/>
+      <c r="I169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -5379,7 +5389,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду32</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду25</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -5395,7 +5405,7 @@
         </is>
       </c>
       <c r="G170" s="3" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="inlineStr"/>
@@ -5406,7 +5416,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду40</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду32</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -5422,7 +5432,7 @@
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="inlineStr"/>
@@ -5433,7 +5443,7 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду50</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду40</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -5449,7 +5459,7 @@
         </is>
       </c>
       <c r="G172" s="3" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="H172" s="3" t="n"/>
       <c r="I172" s="3" t="inlineStr"/>
@@ -5460,7 +5470,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду80</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду50</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -5476,7 +5486,7 @@
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="H173" s="3" t="n"/>
       <c r="I173" s="3" t="inlineStr"/>
@@ -5487,7 +5497,7 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду100</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду80</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -5503,7 +5513,7 @@
         </is>
       </c>
       <c r="G174" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H174" s="3" t="n"/>
       <c r="I174" s="3" t="inlineStr"/>
@@ -5514,7 +5524,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду125</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду100</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -5530,7 +5540,7 @@
         </is>
       </c>
       <c r="G175" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H175" s="3" t="n"/>
       <c r="I175" s="3" t="inlineStr"/>
@@ -5541,7 +5551,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду150</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду125</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -5557,7 +5567,7 @@
         </is>
       </c>
       <c r="G176" s="3" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="H176" s="3" t="n"/>
       <c r="I176" s="3" t="inlineStr"/>
@@ -5568,12 +5578,12 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду80</t>
+          <t>Гильза стальная для прохода через стену/перегородку (труба на 2 типоразмера больше), L по толщине стены + 20 мм, для трубы Ду150</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>, см. узел 3</t>
+          <t>, см. узел 2</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr"/>
@@ -5584,7 +5594,7 @@
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H177" s="3" t="n"/>
       <c r="I177" s="3" t="inlineStr"/>
@@ -5595,7 +5605,7 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду100</t>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду80</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -5611,7 +5621,7 @@
         </is>
       </c>
       <c r="G178" s="3" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H178" s="3" t="n"/>
       <c r="I178" s="3" t="inlineStr"/>
@@ -5622,7 +5632,7 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду150</t>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду100</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -5638,7 +5648,7 @@
         </is>
       </c>
       <c r="G179" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H179" s="3" t="n"/>
       <c r="I179" s="3" t="inlineStr"/>
@@ -5649,26 +5659,26 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Состав огнезащитный терморасширяющийся (герметик) для заделки зазоров в гильзах, EI не ниже предела огнестойкости преграды</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr"/>
+          <t>Гильза стальная для прохода через перекрытие (выступ 30 мм над полом), для трубы Ду150</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>, см. узел 3</t>
+        </is>
+      </c>
       <c r="D180" s="3" t="inlineStr"/>
       <c r="E180" s="3" t="inlineStr"/>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G180" s="3" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="H180" s="3" t="n"/>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>0,25 кг на проход</t>
-        </is>
-      </c>
+      <c r="I180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
@@ -5676,14 +5686,10 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Грунтовка ГФ-021 (1 слой)</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>, ГОСТ 25129-2020</t>
-        </is>
-      </c>
+          <t>Состав огнезащитный терморасширяющийся (герметик) для заделки зазоров в гильзах, EI не ниже предела огнестойкости преграды</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr"/>
       <c r="D181" s="3" t="inlineStr"/>
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3" t="inlineStr">
@@ -5692,12 +5698,12 @@
         </is>
       </c>
       <c r="G181" s="3" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H181" s="3" t="n"/>
       <c r="I181" s="3" t="inlineStr">
         <is>
-          <t>S=692 м²</t>
+          <t>0,25 кг на проход</t>
         </is>
       </c>
     </row>
@@ -5707,12 +5713,12 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Эмаль ПФ-115 красная (2 слоя)</t>
+          <t>Грунтовка ГФ-021 (1 слой)</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>, ГОСТ 6465-76</t>
+          <t>, ГОСТ 25129-2020</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr"/>
@@ -5723,54 +5729,56 @@
         </is>
       </c>
       <c r="G182" s="3" t="n">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="H182" s="3" t="n"/>
-      <c r="I182" s="3" t="inlineStr"/>
+      <c r="I182" s="3" t="inlineStr">
+        <is>
+          <t>S=699 м²</t>
+        </is>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr"/>
-      <c r="B183" s="4" t="inlineStr">
+      <c r="A183" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Эмаль ПФ-115 красная (2 слоя)</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>, ГОСТ 6465-76</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr"/>
+      <c r="E183" s="3" t="inlineStr"/>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr"/>
+      <c r="B184" s="4" t="inlineStr">
         <is>
           <t>8. Автоматическая установка порошкового пожаротушения помещения ВРУ (пом. 06)</t>
         </is>
       </c>
-      <c r="C183" s="3" t="n"/>
-      <c r="D183" s="3" t="n"/>
-      <c r="E183" s="3" t="n"/>
-      <c r="F183" s="3" t="n"/>
-      <c r="G183" s="3" t="n"/>
-      <c r="H183" s="3" t="n"/>
-      <c r="I183" s="3" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>Модуль порошкового пожаротушения закачного типа, масса ОТВ 8 кг, защищаемый объём (класс В) не менее 32 м³, электропуск</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>МПП(Н)-8 (типа «Буран-8» или аналог), ГОСТ Р 53286-2009</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="inlineStr"/>
-      <c r="E184" s="3" t="inlineStr"/>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H184" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I184" s="3" t="inlineStr"/>
+      <c r="C184" s="3" t="n"/>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
+      <c r="I184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n">
@@ -5778,12 +5786,12 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Запас модулей порошкового пожаротушения (100 %)</t>
+          <t>Модуль порошкового пожаротушения закачного типа, масса ОТВ 8 кг, защищаемый объём (класс В) не менее 32 м³, электропуск</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>то же</t>
+          <t>МПП(Н)-8 (типа «Буран-8» или аналог), ГОСТ Р 53286-2009</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr"/>
@@ -5799,11 +5807,7 @@
       <c r="H185" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="I185" s="3" t="inlineStr">
-        <is>
-          <t>хранение на объекте</t>
-        </is>
-      </c>
+      <c r="I185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n">
@@ -5811,34 +5815,30 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Блок управления пожаротушением на одно направление</t>
+          <t>Запас модулей порошкового пожаротушения (100 %)</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>С2000-АСПТ</t>
+          <t>то же</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr"/>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E186" s="3" t="inlineStr"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G186" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>1.1</v>
+        <v>13</v>
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>у входа в пом. 06</t>
+          <t>хранение на объекте</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Извещатель пожарный дымовой оптико-электронный адресно-аналоговый</t>
+          <t>Блок управления пожаротушением на одно направление</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>ДИП-34А-04</t>
+          <t>С2000-АСПТ</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr"/>
@@ -5868,14 +5868,14 @@
         </is>
       </c>
       <c r="G187" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H187" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>пуск по 2 из 3</t>
+          <t>у входа в пом. 06</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Устройство дистанционного пуска «Пуск порошка» (жёлтое, с защитной крышкой)</t>
+          <t>Извещатель пожарный дымовой оптико-электронный адресно-аналоговый</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>ЭДУ 513-3АМ исп. 01</t>
+          <t>ДИП-34А-04</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr"/>
@@ -5905,14 +5905,14 @@
         </is>
       </c>
       <c r="G188" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I188" s="3" t="inlineStr">
         <is>
-          <t>у входа</t>
+          <t>пуск по 2 из 3</t>
         </is>
       </c>
     </row>
@@ -5922,16 +5922,20 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «ПОРОШОК! УХОДИ!» 24 В</t>
+          <t>Устройство дистанционного пуска «Пуск порошка» (жёлтое, с защитной крышкой)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Молния-24</t>
+          <t>ЭДУ 513-3АМ исп. 01</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr"/>
-      <c r="E189" s="3" t="inlineStr"/>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -5941,11 +5945,11 @@
         <v>1</v>
       </c>
       <c r="H189" s="3" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>внутри</t>
+          <t>у входа</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5959,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «ПОРОШОК! НЕ ВХОДИ!» 24 В</t>
+          <t>Табло световое «ПОРОШОК! УХОДИ!» 24 В</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -5978,7 +5982,7 @@
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>над дверью снаружи</t>
+          <t>внутри</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5992,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Табло световое «АВТОМАТИКА ОТКЛЮЧЕНА» 24 В</t>
+          <t>Табло световое «ПОРОШОК! НЕ ВХОДИ!» 24 В</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -6011,7 +6015,7 @@
       </c>
       <c r="I191" s="3" t="inlineStr">
         <is>
-          <t>снаружи</t>
+          <t>над дверью снаружи</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6025,12 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Оповещатель звуковой 24 В, 105 дБ</t>
+          <t>Табло световое «АВТОМАТИКА ОТКЛЮЧЕНА» 24 В</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Маяк-24-3М</t>
+          <t>Молния-24</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr"/>
@@ -6040,11 +6044,11 @@
         <v>1</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>внутри</t>
+          <t>снаружи</t>
         </is>
       </c>
     </row>
@@ -6054,12 +6058,12 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Извещатель магнитоконтактный (контроль закрытия двери)</t>
+          <t>Оповещатель звуковой 24 В, 105 дБ</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>ИО 102-26 «Аякс»</t>
+          <t>Маяк-24-3М</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr"/>
@@ -6073,9 +6077,13 @@
         <v>1</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I193" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>внутри</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n">
@@ -6083,30 +6091,26 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
+          <t>Извещатель магнитоконтактный (контроль закрытия двери)</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>РИП-24 исп. 01</t>
+          <t>ИО 102-26 «Аякс»</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr"/>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
+      <c r="E194" s="3" t="inlineStr"/>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G194" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>11</v>
+        <v>0.1</v>
       </c>
       <c r="I194" s="3" t="inlineStr"/>
     </row>
@@ -6116,80 +6120,76 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>РИП-24 исп. 01</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr"/>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I195" s="3" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
           <t>Коробка коммутационная огнестойкая (Е90)</t>
         </is>
       </c>
-      <c r="C195" s="3" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>КМ-О (4к)-IP41</t>
         </is>
       </c>
-      <c r="D195" s="3" t="inlineStr"/>
-      <c r="E195" s="3" t="inlineStr"/>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="n">
+      <c r="D196" s="3" t="inlineStr"/>
+      <c r="E196" s="3" t="inlineStr"/>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H195" s="3" t="n">
+      <c r="H196" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="I195" s="3" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="3" t="inlineStr"/>
-      <c r="B196" s="4" t="inlineStr">
+      <c r="I196" s="3" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr"/>
+      <c r="B197" s="4" t="inlineStr">
         <is>
           <t>9. Автоматизация систем водяного пожаротушения</t>
         </is>
       </c>
-      <c r="C196" s="3" t="n"/>
-      <c r="D196" s="3" t="n"/>
-      <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
-      <c r="H196" s="3" t="n"/>
-      <c r="I196" s="3" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="3" t="n">
-        <v>183</v>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>Прибор управления насосной станцией пожаротушения (основной, резервный, жокей-насос)</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>Поток-3Н</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr"/>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>ЗАО НВП «Болид»</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" s="3" t="inlineStr">
-        <is>
-          <t>насосная</t>
-        </is>
-      </c>
+      <c r="C197" s="3" t="n"/>
+      <c r="D197" s="3" t="n"/>
+      <c r="E197" s="3" t="n"/>
+      <c r="F197" s="3" t="n"/>
+      <c r="G197" s="3" t="n"/>
+      <c r="H197" s="3" t="n"/>
+      <c r="I197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Шкаф контрольно-пусковой для электродвигателя до 30 кВт, 380 В</t>
+          <t>Прибор управления насосной станцией пожаротушения (основной, резервный, жокей-насос)</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>ШКП-30</t>
+          <t>Поток-3Н</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr"/>
@@ -6217,14 +6217,14 @@
         </is>
       </c>
       <c r="G198" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>Н1, Н2</t>
+          <t>насосная</t>
         </is>
       </c>
     </row>
@@ -6234,12 +6234,12 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Шкаф контрольно-пусковой для электродвигателя до 4 кВт, 380 В</t>
+          <t>Шкаф контрольно-пусковой для электродвигателя до 30 кВт, 380 В</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>ШКП-4</t>
+          <t>ШКП-30</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
@@ -6254,14 +6254,14 @@
         </is>
       </c>
       <c r="G199" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>Н3</t>
+          <t>Н1, Н2</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Контроллер двухпроводной линии связи (адресные устройства ПТ)</t>
+          <t>Шкаф контрольно-пусковой для электродвигателя до 4 кВт, 380 В</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>С2000-КДЛ-2И</t>
+          <t>ШКП-4</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
@@ -6294,11 +6294,11 @@
         <v>1</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>RS-485 к ППКУП «Сириус» (пом. 03)</t>
+          <t>Н3</t>
         </is>
       </c>
     </row>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Адресный расширитель на 2 входа (контроль затворов, дверей шкафов ПК, кнопок «Пуск насосов», аварийного уровня в приямке)</t>
+          <t>Контроллер двухпроводной линии связи (адресные устройства ПТ)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>С2000-АР2 исп. 02</t>
+          <t>С2000-КДЛ-2И</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr"/>
@@ -6328,12 +6328,16 @@
         </is>
       </c>
       <c r="G201" s="3" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I201" s="3" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>RS-485 к ППКУП «Сириус» (пом. 03)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
@@ -6341,12 +6345,12 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
+          <t>Адресный расширитель на 2 входа (контроль затворов, дверей шкафов ПК, кнопок «Пуск насосов», аварийного уровня в приямке)</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>РИП-24 исп. 01</t>
+          <t>С2000-АР2 исп. 02</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr"/>
@@ -6357,14 +6361,14 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G202" s="3" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>11</v>
+        <v>0.05</v>
       </c>
       <c r="I202" s="3" t="inlineStr"/>
     </row>
@@ -6374,74 +6378,76 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Шкаф монтажный навесной 600х600х250 IP54 для приборов автоматики ПТ</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr"/>
+          <t>Источник питания резервированный 24 В, 3 А, с АКБ 2х12 В 17 А·ч</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>РИП-24 исп. 01</t>
+        </is>
+      </c>
       <c r="D203" s="3" t="inlineStr"/>
-      <c r="E203" s="3" t="inlineStr"/>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>ЗАО НВП «Болид»</t>
+        </is>
+      </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G203" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H203" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Шкаф монтажный навесной 600х600х250 IP54 для приборов автоматики ПТ</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr"/>
+      <c r="D204" s="3" t="inlineStr"/>
+      <c r="E204" s="3" t="inlineStr"/>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="I203" s="3" t="inlineStr">
+      <c r="I204" s="3" t="inlineStr">
         <is>
           <t>насосная</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr"/>
-      <c r="B204" s="4" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr"/>
+      <c r="B205" s="4" t="inlineStr">
         <is>
           <t>10. Кабельные изделия (см. кабельный журнал ПТ.КЖ)</t>
         </is>
       </c>
-      <c r="C204" s="3" t="n"/>
-      <c r="D204" s="3" t="n"/>
-      <c r="E204" s="3" t="n"/>
-      <c r="F204" s="3" t="n"/>
-      <c r="G204" s="3" t="n"/>
-      <c r="H204" s="3" t="n"/>
-      <c r="I204" s="3" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>Кабель ВВГнг(А)-FRLS 5х6</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="inlineStr"/>
-      <c r="E205" s="3" t="inlineStr"/>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G205" s="3" t="n">
-        <v>49</v>
-      </c>
+      <c r="C205" s="3" t="n"/>
+      <c r="D205" s="3" t="n"/>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="3" t="n"/>
+      <c r="G205" s="3" t="n"/>
       <c r="H205" s="3" t="n"/>
-      <c r="I205" s="3" t="inlineStr">
-        <is>
-          <t>с запасом 10 %</t>
-        </is>
-      </c>
+      <c r="I205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n">
@@ -6449,7 +6455,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 5х2,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 5х6</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -6480,7 +6486,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 3х1,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 5х2,5</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -6496,7 +6502,7 @@
         </is>
       </c>
       <c r="G207" s="3" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H207" s="3" t="n"/>
       <c r="I207" s="3" t="inlineStr">
@@ -6511,7 +6517,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 4х6</t>
+          <t>Кабель ВВГнг(А)-FRLS 3х1,5</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -6527,7 +6533,7 @@
         </is>
       </c>
       <c r="G208" s="3" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="inlineStr">
@@ -6542,7 +6548,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Кабель ВВГнг(А)-FRLS 4х1,5</t>
+          <t>Кабель ВВГнг(А)-FRLS 4х6</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -6558,7 +6564,7 @@
         </is>
       </c>
       <c r="G209" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H209" s="3" t="n"/>
       <c r="I209" s="3" t="inlineStr">
@@ -6573,12 +6579,12 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 2х2х0,75</t>
+          <t>Кабель ВВГнг(А)-FRLS 4х1,5</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>ВВГнг(А)-FRLS, ГОСТ 31565-2012</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr"/>
@@ -6589,7 +6595,7 @@
         </is>
       </c>
       <c r="G210" s="3" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="H210" s="3" t="n"/>
       <c r="I210" s="3" t="inlineStr">
@@ -6604,7 +6610,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1х2х1,5</t>
+          <t>Кабель КПСнг(А)-FRLS 2х2х0,75</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -6620,7 +6626,7 @@
         </is>
       </c>
       <c r="G211" s="3" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H211" s="3" t="n"/>
       <c r="I211" s="3" t="inlineStr">
@@ -6635,7 +6641,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСнг(А)-FRLS 1х2х0,75</t>
+          <t>Кабель КПСнг(А)-FRLS 1х2х1,5</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -6651,7 +6657,7 @@
         </is>
       </c>
       <c r="G212" s="3" t="n">
-        <v>832</v>
+        <v>41</v>
       </c>
       <c r="H212" s="3" t="n"/>
       <c r="I212" s="3" t="inlineStr">
@@ -6666,12 +6672,12 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>Кабель КПСЭнг(А)-FRLS 1х2х0,75</t>
+          <t>Кабель КПСнг(А)-FRLS 1х2х0,75</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>КПСЭнг(А)-FRLS, ГОСТ 31565-2012</t>
+          <t>КПСнг(А)-FRLS, ГОСТ 31565-2012</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr"/>
@@ -6682,7 +6688,7 @@
         </is>
       </c>
       <c r="G213" s="3" t="n">
-        <v>270</v>
+        <v>832</v>
       </c>
       <c r="H213" s="3" t="n"/>
       <c r="I213" s="3" t="inlineStr">
@@ -6697,10 +6703,14 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Труба гофрированная ПВХ безгалогенная Ø20 мм с протяжкой</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr"/>
+          <t>Кабель КПСЭнг(А)-FRLS 1х2х0,75</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>КПСЭнг(А)-FRLS, ГОСТ 31565-2012</t>
+        </is>
+      </c>
       <c r="D214" s="3" t="inlineStr"/>
       <c r="E214" s="3" t="inlineStr"/>
       <c r="F214" s="3" t="inlineStr">
@@ -6709,12 +6719,12 @@
         </is>
       </c>
       <c r="G214" s="3" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H214" s="3" t="n"/>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>опуски к приборам</t>
+          <t>с запасом 10 %</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6734,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>Металлорукав в ПВХ изоляции Ø25 мм</t>
+          <t>Труба гофрированная ПВХ безгалогенная Ø20 мм с протяжкой</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr"/>
@@ -6736,12 +6746,12 @@
         </is>
       </c>
       <c r="G215" s="3" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="H215" s="3" t="n"/>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>подключение электродвигателей</t>
+          <t>опуски к приборам</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6761,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Лоток кабельный перфорированный 100х50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
+          <t>Металлорукав в ПВХ изоляции Ø25 мм</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr"/>
@@ -6763,10 +6773,37 @@
         </is>
       </c>
       <c r="G216" s="3" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H216" s="3" t="n"/>
       <c r="I216" s="3" t="inlineStr">
+        <is>
+          <t>подключение электродвигателей</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Лоток кабельный перфорированный 100х50 с крышкой, огнестойкая кабельная линия (FRLS)</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr"/>
+      <c r="D217" s="3" t="inlineStr"/>
+      <c r="E217" s="3" t="inlineStr"/>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H217" s="3" t="n"/>
+      <c r="I217" s="3" t="inlineStr">
         <is>
           <t>пом. 06 – тамбур 92 – пом. 05 – насосная</t>
         </is>
@@ -6818,10 +6855,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -6834,10 +6871,10 @@
         <v>80</v>
       </c>
       <c r="C3" t="n">
-        <v>116</v>
+        <v>142.7</v>
       </c>
       <c r="D3" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
@@ -6850,7 +6887,7 @@
         <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>214.5</v>
+        <v>214.3</v>
       </c>
       <c r="D4" t="n">
         <v>226</v>
@@ -7713,7 +7750,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Кольцевая ДПЛС: С2000-АР2 шкафов ПК (30 шт.), затворов и ШУД (7 шт.)</t>
+          <t>Кольцевая ДПЛС: С2000-АР2 шкафов ПК (36 шт.), затворов и ШУД (7 шт.)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
